--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -273,7 +273,7 @@
     <t>#C0CA33</t>
   </si>
   <si>
-    <t>1040010001&amp;1040020001&amp;1020010001&amp;1030010001&amp;1030020001</t>
+    <t>1040010001&amp;1010020002&amp;1020010001&amp;1030010001&amp;1030020001</t>
   </si>
   <si>
     <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1020020001&amp;1020030001</t>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>id</t>
   </si>
@@ -306,22 +306,31 @@
     <t>#FBC02D</t>
   </si>
   <si>
+    <t>1040010001&amp;1010020002&amp;1020010001&amp;1030010001&amp;1030020001&amp;1030030001&amp;1031020001</t>
+  </si>
+  <si>
+    <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1020020001&amp;1020030001&amp;1031030001&amp;1031040001</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>5-6</t>
+  </si>
+  <si>
+    <t>6-10</t>
+  </si>
+  <si>
+    <t>500-550</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度5</t>
+  </si>
+  <si>
+    <t>#FB8C00</t>
+  </si>
+  <si>
     <t>1010010001&amp;1010010001</t>
-  </si>
-  <si>
-    <t>5-6</t>
-  </si>
-  <si>
-    <t>6-10</t>
-  </si>
-  <si>
-    <t>500-550</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度5</t>
-  </si>
-  <si>
-    <t>#FB8C00</t>
   </si>
   <si>
     <t>8-11</t>
@@ -2145,13 +2154,13 @@
         <v>97</v>
       </c>
       <c r="G8" s="51" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H8" s="51">
         <v>5</v>
       </c>
-      <c r="I8" s="51">
-        <v>50</v>
+      <c r="I8" s="51" t="s">
+        <v>60</v>
       </c>
       <c r="J8" s="51">
         <v>60</v>
@@ -2159,29 +2168,29 @@
       <c r="K8" s="51">
         <v>1</v>
       </c>
-      <c r="L8" s="51">
-        <v>2</v>
-      </c>
-      <c r="M8" s="51">
-        <v>3</v>
-      </c>
-      <c r="N8" s="51">
-        <v>1</v>
+      <c r="L8" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="51" t="s">
+        <v>67</v>
       </c>
       <c r="O8" s="51" t="s">
         <v>93</v>
       </c>
       <c r="P8" s="54" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="Q8" s="51" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R8" s="51">
         <v>5</v>
       </c>
       <c r="S8" s="51" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T8" s="51">
         <v>2</v>
@@ -2196,10 +2205,10 @@
         <v>5</v>
       </c>
       <c r="X8" s="51" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="Y8" s="50" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9">
@@ -2219,10 +2228,10 @@
         <v>55</v>
       </c>
       <c r="F9" s="51" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H9" s="51">
         <v>6</v>
@@ -2246,19 +2255,19 @@
         <v>1</v>
       </c>
       <c r="O9" s="51" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q9" s="51" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="R9" s="51">
         <v>6</v>
       </c>
       <c r="S9" s="51" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="T9" s="51">
         <v>3</v>
@@ -2273,10 +2282,10 @@
         <v>6</v>
       </c>
       <c r="X9" s="51" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Y9" s="50" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -2296,10 +2305,10 @@
         <v>55</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H10" s="51">
         <v>7</v>
@@ -2323,19 +2332,19 @@
         <v>1</v>
       </c>
       <c r="O10" s="51" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="P10" s="51" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q10" s="51" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="R10" s="51">
         <v>7</v>
       </c>
       <c r="S10" s="51" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="T10" s="51">
         <v>3</v>
@@ -2350,10 +2359,10 @@
         <v>7</v>
       </c>
       <c r="X10" s="51" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Y10" s="50" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -2373,10 +2382,10 @@
         <v>55</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H11" s="51">
         <v>8</v>
@@ -2400,19 +2409,19 @@
         <v>1</v>
       </c>
       <c r="O11" s="51" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q11" s="51" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R11" s="51">
         <v>8</v>
       </c>
       <c r="S11" s="51" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="T11" s="51">
         <v>3</v>
@@ -2427,10 +2436,10 @@
         <v>8</v>
       </c>
       <c r="X11" s="51" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="Y11" s="50" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12">
@@ -2450,10 +2459,10 @@
         <v>55</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G12" s="51" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H12" s="51">
         <v>9</v>
@@ -2477,19 +2486,19 @@
         <v>1</v>
       </c>
       <c r="O12" s="51" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q12" s="51" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="R12" s="51">
         <v>9</v>
       </c>
       <c r="S12" s="51" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="T12" s="51">
         <v>4</v>
@@ -2504,10 +2513,10 @@
         <v>9</v>
       </c>
       <c r="X12" s="51" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="Y12" s="50" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -2527,10 +2536,10 @@
         <v>55</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H13" s="51">
         <v>10</v>
@@ -2554,19 +2563,19 @@
         <v>1</v>
       </c>
       <c r="O13" s="51" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Q13" s="51" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="R13" s="51">
         <v>10</v>
       </c>
       <c r="S13" s="51" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="T13" s="51">
         <v>4</v>
@@ -2581,10 +2590,10 @@
         <v>10</v>
       </c>
       <c r="X13" s="51" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Y13" s="50" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <si>
     <t>id</t>
   </si>
@@ -306,7 +306,7 @@
     <t>#FBC02D</t>
   </si>
   <si>
-    <t>1040010001&amp;1010020002&amp;1020010001&amp;1030010001&amp;1030020001&amp;1030030001&amp;1031020001</t>
+    <t>1040010001&amp;1010020002&amp;1020010001&amp;1030010001&amp;1030020001&amp;1030030001&amp;1030040001</t>
   </si>
   <si>
     <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1020020001&amp;1020030001&amp;1031030001&amp;1031040001</t>
@@ -330,28 +330,43 @@
     <t>#FB8C00</t>
   </si>
   <si>
+    <t>1040010001&amp;1010020002&amp;1030010001&amp;1030020001&amp;1030030001&amp;1030040001&amp;1020020002&amp;1020030002</t>
+  </si>
+  <si>
+    <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1031030001&amp;1031040001</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>8-11</t>
+  </si>
+  <si>
+    <t>5-10</t>
+  </si>
+  <si>
+    <t>600-650</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度6</t>
+  </si>
+  <si>
+    <t>#F4511E</t>
+  </si>
+  <si>
     <t>1010010001&amp;1010010001</t>
   </si>
   <si>
-    <t>8-11</t>
+    <t>9-12</t>
   </si>
   <si>
     <t>1-6</t>
-  </si>
-  <si>
-    <t>5-10</t>
-  </si>
-  <si>
-    <t>600-650</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度6</t>
-  </si>
-  <si>
-    <t>#F4511E</t>
-  </si>
-  <si>
-    <t>9-12</t>
   </si>
   <si>
     <t>4-10</t>
@@ -2231,13 +2246,13 @@
         <v>105</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H9" s="51">
         <v>6</v>
       </c>
-      <c r="I9" s="51">
-        <v>60</v>
+      <c r="I9" s="51" t="s">
+        <v>107</v>
       </c>
       <c r="J9" s="51">
         <v>60</v>
@@ -2245,29 +2260,29 @@
       <c r="K9" s="51">
         <v>1</v>
       </c>
-      <c r="L9" s="51">
-        <v>2</v>
-      </c>
-      <c r="M9" s="51">
-        <v>3.5</v>
-      </c>
-      <c r="N9" s="51">
-        <v>1</v>
+      <c r="L9" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="M9" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="51" t="s">
+        <v>109</v>
       </c>
       <c r="O9" s="51" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="51" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="R9" s="51">
         <v>6</v>
       </c>
       <c r="S9" s="51" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="T9" s="51">
         <v>3</v>
@@ -2282,10 +2297,10 @@
         <v>6</v>
       </c>
       <c r="X9" s="51" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Y9" s="50" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -2305,10 +2320,10 @@
         <v>55</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G10" s="51" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H10" s="51">
         <v>7</v>
@@ -2332,19 +2347,19 @@
         <v>1</v>
       </c>
       <c r="O10" s="51" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="P10" s="51" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="Q10" s="51" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="R10" s="51">
         <v>7</v>
       </c>
       <c r="S10" s="51" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="T10" s="51">
         <v>3</v>
@@ -2359,10 +2374,10 @@
         <v>7</v>
       </c>
       <c r="X10" s="51" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Y10" s="50" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
@@ -2382,10 +2397,10 @@
         <v>55</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H11" s="51">
         <v>8</v>
@@ -2409,19 +2424,19 @@
         <v>1</v>
       </c>
       <c r="O11" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="P11" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="P11" s="51" t="s">
-        <v>107</v>
-      </c>
       <c r="Q11" s="51" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="R11" s="51">
         <v>8</v>
       </c>
       <c r="S11" s="51" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="T11" s="51">
         <v>3</v>
@@ -2436,10 +2451,10 @@
         <v>8</v>
       </c>
       <c r="X11" s="51" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="Y11" s="50" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12">
@@ -2459,10 +2474,10 @@
         <v>55</v>
       </c>
       <c r="F12" s="51" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G12" s="51" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H12" s="51">
         <v>9</v>
@@ -2486,19 +2501,19 @@
         <v>1</v>
       </c>
       <c r="O12" s="51" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="Q12" s="51" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="R12" s="51">
         <v>9</v>
       </c>
       <c r="S12" s="51" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="T12" s="51">
         <v>4</v>
@@ -2513,10 +2528,10 @@
         <v>9</v>
       </c>
       <c r="X12" s="51" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="Y12" s="50" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2536,10 +2551,10 @@
         <v>55</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="H13" s="51">
         <v>10</v>
@@ -2563,19 +2578,19 @@
         <v>1</v>
       </c>
       <c r="O13" s="51" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="Q13" s="51" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="R13" s="51">
         <v>10</v>
       </c>
       <c r="S13" s="51" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="T13" s="51">
         <v>4</v>
@@ -2590,10 +2605,10 @@
         <v>10</v>
       </c>
       <c r="X13" s="51" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="Y13" s="50" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
   <si>
     <t>id</t>
   </si>
@@ -333,7 +333,7 @@
     <t>1040010001&amp;1010020002&amp;1030010001&amp;1030020001&amp;1030030001&amp;1030040001&amp;1020020002&amp;1020030002</t>
   </si>
   <si>
-    <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1031030001&amp;1031040001</t>
+    <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1031030001&amp;1031040001&amp;1041030001</t>
   </si>
   <si>
     <t>70</t>
@@ -360,25 +360,37 @@
     <t>#F4511E</t>
   </si>
   <si>
+    <t>1040010001&amp;1030010001&amp;1030020001&amp;1030030001&amp;1030040001&amp;1020020002&amp;1020030002&amp;1041010002&amp;1041020002</t>
+  </si>
+  <si>
+    <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1031030001&amp;1031040001&amp;1041030001&amp;1031050001</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>9-12</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>4-10</t>
+  </si>
+  <si>
+    <t>700-750</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度7</t>
+  </si>
+  <si>
+    <t>#E53935</t>
+  </si>
+  <si>
     <t>1010010001&amp;1010010001</t>
-  </si>
-  <si>
-    <t>9-12</t>
-  </si>
-  <si>
-    <t>1-6</t>
-  </si>
-  <si>
-    <t>4-10</t>
-  </si>
-  <si>
-    <t>700-750</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度7</t>
-  </si>
-  <si>
-    <t>#E53935</t>
   </si>
   <si>
     <t>9-13</t>
@@ -430,12 +442,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="19">
     <font>
       <sz val="11"/>
@@ -1617,70 +1624,70 @@
       <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="51" t="s">
+      <c r="L1" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="51" t="s">
+      <c r="M1" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="51" t="s">
+      <c r="N1" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="51" t="s">
+      <c r="O1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="Q1" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="51" t="s">
+      <c r="R1" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="51" t="s">
+      <c r="S1" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="51" t="s">
+      <c r="T1" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="51" t="s">
+      <c r="U1" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="51" t="s">
+      <c r="V1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="51" t="s">
+      <c r="W1" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="51" t="s">
+      <c r="X1" s="50" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="50" t="s">
@@ -1694,70 +1701,70 @@
       <c r="B2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="L2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="51" t="s">
+      <c r="M2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="51" t="s">
+      <c r="N2" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="51" t="s">
+      <c r="O2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="51" t="s">
+      <c r="P2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="51" t="s">
+      <c r="Q2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="R2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="S2" s="51" t="s">
+      <c r="S2" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="51" t="s">
+      <c r="T2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="51" t="s">
+      <c r="U2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="51" t="s">
+      <c r="V2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="51" t="s">
+      <c r="W2" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="51" t="s">
+      <c r="X2" s="50" t="s">
         <v>27</v>
       </c>
       <c r="Y2" s="50" t="s">
@@ -1771,70 +1778,70 @@
       <c r="B3" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="L3" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="51" t="s">
+      <c r="M3" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="51" t="s">
+      <c r="N3" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="51" t="s">
+      <c r="O3" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="51" t="s">
+      <c r="P3" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="51" t="s">
+      <c r="Q3" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="51" t="s">
+      <c r="R3" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="51" t="s">
+      <c r="S3" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="T3" s="51" t="s">
+      <c r="T3" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="51" t="s">
+      <c r="U3" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="V3" s="51" t="s">
+      <c r="V3" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="W3" s="51" t="s">
+      <c r="W3" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="X3" s="51" t="s">
+      <c r="X3" s="50" t="s">
         <v>52</v>
       </c>
       <c r="Y3" s="50" t="s">
@@ -1848,70 +1855,70 @@
       <c r="B4" s="50">
         <v>1</v>
       </c>
-      <c r="C4" s="51">
-        <v>1</v>
-      </c>
-      <c r="D4" s="51" t="s">
+      <c r="C4" s="50">
+        <v>1</v>
+      </c>
+      <c r="D4" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="J4" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="51">
-        <v>1</v>
-      </c>
-      <c r="L4" s="51" t="s">
+      <c r="K4" s="50">
+        <v>1</v>
+      </c>
+      <c r="L4" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="51">
-        <v>1</v>
-      </c>
-      <c r="N4" s="51">
-        <v>1</v>
-      </c>
-      <c r="O4" s="51">
+      <c r="M4" s="50">
+        <v>1</v>
+      </c>
+      <c r="N4" s="50">
+        <v>1</v>
+      </c>
+      <c r="O4" s="50">
         <v>5</v>
       </c>
-      <c r="P4" s="51">
+      <c r="P4" s="50">
         <v>2</v>
       </c>
-      <c r="Q4" s="51">
+      <c r="Q4" s="50">
         <v>10</v>
       </c>
-      <c r="R4" s="51">
+      <c r="R4" s="50">
         <v>1</v>
       </c>
       <c r="S4" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="T4" s="51">
-        <v>1</v>
-      </c>
-      <c r="U4" s="51">
+      <c r="T4" s="50">
+        <v>1</v>
+      </c>
+      <c r="U4" s="50">
         <v>10</v>
       </c>
-      <c r="V4" s="51">
+      <c r="V4" s="50">
         <v>50</v>
       </c>
-      <c r="W4" s="51">
-        <v>1</v>
-      </c>
-      <c r="X4" s="51" t="s">
+      <c r="W4" s="50">
+        <v>1</v>
+      </c>
+      <c r="X4" s="50" t="s">
         <v>62</v>
       </c>
       <c r="Y4" s="50" t="s">
@@ -1925,70 +1932,70 @@
       <c r="B5" s="50">
         <v>1</v>
       </c>
-      <c r="C5" s="51">
+      <c r="C5" s="50">
         <v>2</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D5" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="G5" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="50">
         <v>20</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="50">
         <v>60</v>
       </c>
-      <c r="K5" s="51">
-        <v>1</v>
-      </c>
-      <c r="L5" s="51" t="s">
+      <c r="K5" s="50">
+        <v>1</v>
+      </c>
+      <c r="L5" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="M5" s="51" t="s">
+      <c r="M5" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="51" t="s">
+      <c r="N5" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="O5" s="51" t="s">
+      <c r="O5" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="50">
         <v>3</v>
       </c>
       <c r="Q5" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="50">
         <v>2</v>
       </c>
-      <c r="S5" s="51" t="s">
+      <c r="S5" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="T5" s="51">
-        <v>1</v>
-      </c>
-      <c r="U5" s="51">
+      <c r="T5" s="50">
+        <v>1</v>
+      </c>
+      <c r="U5" s="50">
         <v>20</v>
       </c>
-      <c r="V5" s="51">
+      <c r="V5" s="50">
         <v>100</v>
       </c>
-      <c r="W5" s="51">
+      <c r="W5" s="50">
         <v>2</v>
       </c>
-      <c r="X5" s="51" t="s">
+      <c r="X5" s="50" t="s">
         <v>73</v>
       </c>
       <c r="Y5" s="50" t="s">
@@ -2002,70 +2009,70 @@
       <c r="B6" s="50">
         <v>1</v>
       </c>
-      <c r="C6" s="51">
+      <c r="C6" s="50">
         <v>3</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="51" t="s">
+      <c r="G6" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="51">
+      <c r="H6" s="50">
         <v>3</v>
       </c>
-      <c r="I6" s="51" t="s">
+      <c r="I6" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="51">
+      <c r="J6" s="50">
         <v>60</v>
       </c>
-      <c r="K6" s="51">
-        <v>1</v>
-      </c>
-      <c r="L6" s="51" t="s">
+      <c r="K6" s="50">
+        <v>1</v>
+      </c>
+      <c r="L6" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="M6" s="51" t="s">
+      <c r="M6" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="51" t="s">
+      <c r="N6" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="O6" s="51" t="s">
+      <c r="O6" s="50" t="s">
         <v>80</v>
       </c>
       <c r="P6" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="Q6" s="51" t="s">
+      <c r="Q6" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="R6" s="51">
+      <c r="R6" s="50">
         <v>3</v>
       </c>
-      <c r="S6" s="51" t="s">
+      <c r="S6" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="T6" s="51">
+      <c r="T6" s="50">
         <v>2</v>
       </c>
-      <c r="U6" s="51">
+      <c r="U6" s="50">
         <v>30</v>
       </c>
-      <c r="V6" s="51">
+      <c r="V6" s="50">
         <v>150</v>
       </c>
-      <c r="W6" s="51">
+      <c r="W6" s="50">
         <v>3</v>
       </c>
-      <c r="X6" s="51" t="s">
+      <c r="X6" s="50" t="s">
         <v>84</v>
       </c>
       <c r="Y6" s="50" t="s">
@@ -2079,70 +2086,70 @@
       <c r="B7" s="50">
         <v>1</v>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="50">
         <v>4</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D7" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="51" t="s">
+      <c r="F7" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="51" t="s">
+      <c r="G7" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="H7" s="51">
+      <c r="H7" s="50">
         <v>4</v>
       </c>
-      <c r="I7" s="51" t="s">
+      <c r="I7" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="51">
+      <c r="J7" s="50">
         <v>60</v>
       </c>
-      <c r="K7" s="51">
-        <v>1</v>
-      </c>
-      <c r="L7" s="51" t="s">
+      <c r="K7" s="50">
+        <v>1</v>
+      </c>
+      <c r="L7" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="M7" s="51" t="s">
+      <c r="M7" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="51" t="s">
+      <c r="N7" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="O7" s="51" t="s">
+      <c r="O7" s="50" t="s">
         <v>91</v>
       </c>
       <c r="P7" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="Q7" s="51" t="s">
+      <c r="Q7" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="R7" s="51">
+      <c r="R7" s="50">
         <v>4</v>
       </c>
-      <c r="S7" s="51" t="s">
+      <c r="S7" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="T7" s="51">
+      <c r="T7" s="50">
         <v>2</v>
       </c>
-      <c r="U7" s="51">
+      <c r="U7" s="50">
         <v>40</v>
       </c>
-      <c r="V7" s="51">
+      <c r="V7" s="50">
         <v>200</v>
       </c>
-      <c r="W7" s="51">
+      <c r="W7" s="50">
         <v>4</v>
       </c>
-      <c r="X7" s="51" t="s">
+      <c r="X7" s="50" t="s">
         <v>95</v>
       </c>
       <c r="Y7" s="50" t="s">
@@ -2156,70 +2163,70 @@
       <c r="B8" s="50">
         <v>1</v>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="50">
         <v>5</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="D8" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="F8" s="50" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="51" t="s">
+      <c r="G8" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="H8" s="51">
+      <c r="H8" s="50">
         <v>5</v>
       </c>
-      <c r="I8" s="51" t="s">
+      <c r="I8" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="51">
+      <c r="J8" s="50">
         <v>60</v>
       </c>
-      <c r="K8" s="51">
-        <v>1</v>
-      </c>
-      <c r="L8" s="51" t="s">
+      <c r="K8" s="50">
+        <v>1</v>
+      </c>
+      <c r="L8" s="50" t="s">
         <v>99</v>
       </c>
-      <c r="M8" s="51" t="s">
+      <c r="M8" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="N8" s="51" t="s">
+      <c r="N8" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="O8" s="51" t="s">
+      <c r="O8" s="50" t="s">
         <v>93</v>
       </c>
       <c r="P8" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="Q8" s="51" t="s">
+      <c r="Q8" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="R8" s="51">
+      <c r="R8" s="50">
         <v>5</v>
       </c>
-      <c r="S8" s="51" t="s">
+      <c r="S8" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="T8" s="51">
+      <c r="T8" s="50">
         <v>2</v>
       </c>
-      <c r="U8" s="51">
+      <c r="U8" s="50">
         <v>50</v>
       </c>
-      <c r="V8" s="51">
+      <c r="V8" s="50">
         <v>250</v>
       </c>
-      <c r="W8" s="51">
+      <c r="W8" s="50">
         <v>5</v>
       </c>
-      <c r="X8" s="51" t="s">
+      <c r="X8" s="50" t="s">
         <v>103</v>
       </c>
       <c r="Y8" s="50" t="s">
@@ -2233,70 +2240,70 @@
       <c r="B9" s="50">
         <v>1</v>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="50">
         <v>6</v>
       </c>
-      <c r="D9" s="51" t="s">
+      <c r="D9" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="51" t="s">
+      <c r="F9" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="51" t="s">
+      <c r="G9" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="H9" s="51">
+      <c r="H9" s="50">
         <v>6</v>
       </c>
-      <c r="I9" s="51" t="s">
+      <c r="I9" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="J9" s="51">
+      <c r="J9" s="50">
         <v>60</v>
       </c>
-      <c r="K9" s="51">
-        <v>1</v>
-      </c>
-      <c r="L9" s="51" t="s">
+      <c r="K9" s="50">
+        <v>1</v>
+      </c>
+      <c r="L9" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="M9" s="51" t="s">
+      <c r="M9" s="50" t="s">
         <v>58</v>
       </c>
-      <c r="N9" s="51" t="s">
+      <c r="N9" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="O9" s="51" t="s">
+      <c r="O9" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="P9" s="51" t="s">
+      <c r="P9" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="Q9" s="51" t="s">
+      <c r="Q9" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="R9" s="51">
+      <c r="R9" s="50">
         <v>6</v>
       </c>
-      <c r="S9" s="51" t="s">
+      <c r="S9" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="T9" s="51">
+      <c r="T9" s="50">
         <v>3</v>
       </c>
-      <c r="U9" s="51">
+      <c r="U9" s="50">
         <v>60</v>
       </c>
-      <c r="V9" s="51">
+      <c r="V9" s="50">
         <v>300</v>
       </c>
-      <c r="W9" s="51">
+      <c r="W9" s="50">
         <v>6</v>
       </c>
-      <c r="X9" s="51" t="s">
+      <c r="X9" s="50" t="s">
         <v>113</v>
       </c>
       <c r="Y9" s="50" t="s">
@@ -2310,74 +2317,74 @@
       <c r="B10" s="50">
         <v>1</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="50">
         <v>7</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D10" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="51" t="s">
+      <c r="E10" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="51" t="s">
+      <c r="F10" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="H10" s="51">
+      <c r="G10" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="H10" s="50">
         <v>7</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="J10" s="50">
+        <v>60</v>
+      </c>
+      <c r="K10" s="50">
+        <v>1</v>
+      </c>
+      <c r="L10" s="50" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="O10" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="P10" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q10" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="R10" s="50">
+        <v>7</v>
+      </c>
+      <c r="S10" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="T10" s="50">
+        <v>3</v>
+      </c>
+      <c r="U10" s="50">
         <v>70</v>
       </c>
-      <c r="J10" s="51">
-        <v>60</v>
-      </c>
-      <c r="K10" s="51">
-        <v>1</v>
-      </c>
-      <c r="L10" s="51">
-        <v>2</v>
-      </c>
-      <c r="M10" s="51">
-        <v>4</v>
-      </c>
-      <c r="N10" s="51">
-        <v>1</v>
-      </c>
-      <c r="O10" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="P10" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q10" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="R10" s="51">
+      <c r="V10" s="50">
+        <v>350</v>
+      </c>
+      <c r="W10" s="50">
         <v>7</v>
       </c>
-      <c r="S10" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="T10" s="51">
-        <v>3</v>
-      </c>
-      <c r="U10" s="51">
-        <v>70</v>
-      </c>
-      <c r="V10" s="51">
-        <v>350</v>
-      </c>
-      <c r="W10" s="51">
-        <v>7</v>
-      </c>
-      <c r="X10" s="51" t="s">
-        <v>120</v>
+      <c r="X10" s="50" t="s">
+        <v>123</v>
       </c>
       <c r="Y10" s="50" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -2387,74 +2394,74 @@
       <c r="B11" s="50">
         <v>1</v>
       </c>
-      <c r="C11" s="51">
+      <c r="C11" s="50">
         <v>8</v>
       </c>
-      <c r="D11" s="51" t="s">
+      <c r="D11" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="51" t="s">
+      <c r="E11" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="G11" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="H11" s="51">
+      <c r="F11" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="50">
         <v>8</v>
       </c>
-      <c r="I11" s="51">
+      <c r="I11" s="50">
         <v>80</v>
       </c>
-      <c r="J11" s="51">
+      <c r="J11" s="50">
         <v>60</v>
       </c>
-      <c r="K11" s="51">
-        <v>1</v>
-      </c>
-      <c r="L11" s="51">
+      <c r="K11" s="50">
+        <v>1</v>
+      </c>
+      <c r="L11" s="50">
         <v>2</v>
       </c>
-      <c r="M11" s="51">
+      <c r="M11" s="50">
         <v>4.5</v>
       </c>
-      <c r="N11" s="51">
-        <v>1</v>
-      </c>
-      <c r="O11" s="51" t="s">
-        <v>122</v>
-      </c>
-      <c r="P11" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q11" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="R11" s="51">
+      <c r="N11" s="50">
+        <v>1</v>
+      </c>
+      <c r="O11" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="P11" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q11" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="R11" s="50">
         <v>8</v>
       </c>
-      <c r="S11" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="T11" s="51">
+      <c r="S11" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="T11" s="50">
         <v>3</v>
       </c>
-      <c r="U11" s="51">
+      <c r="U11" s="50">
         <v>80</v>
       </c>
-      <c r="V11" s="51">
+      <c r="V11" s="50">
         <v>400</v>
       </c>
-      <c r="W11" s="51">
+      <c r="W11" s="50">
         <v>8</v>
       </c>
-      <c r="X11" s="51" t="s">
-        <v>125</v>
+      <c r="X11" s="50" t="s">
+        <v>129</v>
       </c>
       <c r="Y11" s="50" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2464,74 +2471,74 @@
       <c r="B12" s="50">
         <v>1</v>
       </c>
-      <c r="C12" s="51">
+      <c r="C12" s="50">
         <v>9</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="51">
+      <c r="F12" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="H12" s="50">
         <v>9</v>
       </c>
-      <c r="I12" s="51">
+      <c r="I12" s="50">
         <v>90</v>
       </c>
-      <c r="J12" s="51">
+      <c r="J12" s="50">
         <v>60</v>
       </c>
-      <c r="K12" s="51">
-        <v>1</v>
-      </c>
-      <c r="L12" s="51">
+      <c r="K12" s="50">
+        <v>1</v>
+      </c>
+      <c r="L12" s="50">
         <v>2</v>
       </c>
-      <c r="M12" s="51">
+      <c r="M12" s="50">
         <v>5</v>
       </c>
-      <c r="N12" s="51">
-        <v>1</v>
-      </c>
-      <c r="O12" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="P12" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q12" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="R12" s="51">
+      <c r="N12" s="50">
+        <v>1</v>
+      </c>
+      <c r="O12" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="P12" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q12" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="R12" s="50">
         <v>9</v>
       </c>
-      <c r="S12" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="T12" s="51">
+      <c r="S12" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="T12" s="50">
         <v>4</v>
       </c>
-      <c r="U12" s="51">
+      <c r="U12" s="50">
         <v>90</v>
       </c>
-      <c r="V12" s="51">
+      <c r="V12" s="50">
         <v>450</v>
       </c>
-      <c r="W12" s="51">
+      <c r="W12" s="50">
         <v>9</v>
       </c>
-      <c r="X12" s="51" t="s">
-        <v>130</v>
+      <c r="X12" s="50" t="s">
+        <v>134</v>
       </c>
       <c r="Y12" s="50" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2541,74 +2548,74 @@
       <c r="B13" s="50">
         <v>1</v>
       </c>
-      <c r="C13" s="51">
+      <c r="C13" s="50">
         <v>10</v>
       </c>
-      <c r="D13" s="51" t="s">
+      <c r="D13" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="51" t="s">
+      <c r="E13" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="H13" s="51">
+      <c r="F13" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="H13" s="50">
         <v>10</v>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="50">
         <v>100</v>
       </c>
-      <c r="J13" s="51">
+      <c r="J13" s="50">
         <v>60</v>
       </c>
-      <c r="K13" s="51">
-        <v>1</v>
-      </c>
-      <c r="L13" s="51">
+      <c r="K13" s="50">
+        <v>1</v>
+      </c>
+      <c r="L13" s="50">
         <v>2</v>
       </c>
-      <c r="M13" s="51">
+      <c r="M13" s="50">
         <v>5.5</v>
       </c>
-      <c r="N13" s="51">
-        <v>1</v>
-      </c>
-      <c r="O13" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="P13" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q13" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="R13" s="51">
+      <c r="N13" s="50">
+        <v>1</v>
+      </c>
+      <c r="O13" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="P13" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q13" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="R13" s="50">
         <v>10</v>
       </c>
-      <c r="S13" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="T13" s="51">
+      <c r="S13" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="T13" s="50">
         <v>4</v>
       </c>
-      <c r="U13" s="51">
+      <c r="U13" s="50">
         <v>100</v>
       </c>
-      <c r="V13" s="51">
+      <c r="V13" s="50">
         <v>500</v>
       </c>
-      <c r="W13" s="51">
+      <c r="W13" s="50">
         <v>10</v>
       </c>
-      <c r="X13" s="51" t="s">
-        <v>135</v>
+      <c r="X13" s="50" t="s">
+        <v>139</v>
       </c>
       <c r="Y13" s="50" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -1,19 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\DemonLordRoguelike\Demon Lord Roguelike\Assets\Data\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="141">
   <si>
     <t>id</t>
   </si>
@@ -441,13 +460,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -455,6 +480,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -462,12 +488,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -475,6 +503,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -482,6 +511,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -489,6 +519,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -496,6 +527,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -503,12 +535,14 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -516,6 +550,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -523,6 +558,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -530,12 +566,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -543,30 +581,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1020,166 +1063,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1235,74 +1128,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1591,1056 +1421,1053 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Y13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Y81"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="16" customWidth="1" style="51"/>
-    <col min="4" max="4" width="17.125" customWidth="1" style="51"/>
-    <col min="5" max="5" width="36.5" customWidth="1" style="51"/>
-    <col min="6" max="6" width="23.75" customWidth="1" style="51"/>
-    <col min="7" max="7" width="18.375" customWidth="1" style="51"/>
-    <col min="8" max="8" width="31.875" customWidth="1" style="51"/>
-    <col min="9" max="9" width="18.25" customWidth="1" style="51"/>
-    <col min="10" max="16" width="16" customWidth="1" style="51"/>
-    <col min="17" max="17" width="12.25" customWidth="1" style="51"/>
-    <col min="18" max="18" width="12.875" customWidth="1" style="51"/>
-    <col min="19" max="19" width="27.125" customWidth="1" style="51"/>
-    <col min="20" max="20" width="17.375" customWidth="1" style="51"/>
-    <col min="21" max="21" width="36.875" customWidth="1" style="51"/>
-    <col min="22" max="22" width="29.375" customWidth="1" style="51"/>
-    <col min="23" max="23" width="42.875" customWidth="1" style="51"/>
-    <col min="24" max="24" width="25.125" customWidth="1" style="51"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
+    <col min="10" max="16" width="16" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.25" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="27.125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="17.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="36.875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="29.375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="42.875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="50" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="50" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="50" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="50" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="50" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="50" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="50" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="50" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="50" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="50" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="50" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="50" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="50" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="50" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="50" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="50" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="50" t="s">
+    <row r="2" spans="1:25">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="E2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="F2" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="50" t="s">
+      <c r="H2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="50" t="s">
+      <c r="J2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="50" t="s">
+      <c r="K2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="50" t="s">
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="50" t="s">
+      <c r="M2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="50" t="s">
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="50" t="s">
+      <c r="O2" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="50" t="s">
+      <c r="P2" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="50" t="s">
+      <c r="Q2" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="50" t="s">
+      <c r="R2" t="s">
         <v>26</v>
       </c>
-      <c r="S2" s="50" t="s">
+      <c r="S2" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="50" t="s">
+      <c r="T2" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="50" t="s">
+      <c r="U2" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="50" t="s">
+      <c r="V2" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="50" t="s">
+      <c r="W2" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="50" t="s">
+      <c r="X2" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="50" t="s">
+      <c r="Y2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="50" t="s">
+    <row r="3" spans="1:25">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="50" t="s">
+      <c r="I3" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="50" t="s">
+      <c r="J3" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="K3" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="50" t="s">
+      <c r="L3" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="50" t="s">
+      <c r="M3" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="50" t="s">
+      <c r="N3" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="50" t="s">
+      <c r="O3" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="50" t="s">
+      <c r="P3" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="50" t="s">
+      <c r="Q3" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="50" t="s">
+      <c r="R3" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="50" t="s">
+      <c r="S3" t="s">
         <v>47</v>
       </c>
-      <c r="T3" s="50" t="s">
+      <c r="T3" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="50" t="s">
+      <c r="U3" t="s">
         <v>49</v>
       </c>
-      <c r="V3" s="50" t="s">
+      <c r="V3" t="s">
         <v>50</v>
       </c>
-      <c r="W3" s="50" t="s">
+      <c r="W3" t="s">
         <v>51</v>
       </c>
-      <c r="X3" s="50" t="s">
+      <c r="X3" t="s">
         <v>52</v>
       </c>
-      <c r="Y3" s="50" t="s">
+      <c r="Y3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="50">
+    <row r="4" spans="1:25">
+      <c r="A4">
         <v>1000001</v>
       </c>
-      <c r="B4" s="50">
-        <v>1</v>
-      </c>
-      <c r="C4" s="50">
-        <v>1</v>
-      </c>
-      <c r="D4" s="50" t="s">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="50" t="s">
+      <c r="G4" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="50" t="s">
+      <c r="H4" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="50" t="s">
+      <c r="I4" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="50" t="s">
+      <c r="J4" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="50">
-        <v>1</v>
-      </c>
-      <c r="L4" s="50" t="s">
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="50">
-        <v>1</v>
-      </c>
-      <c r="N4" s="50">
-        <v>1</v>
-      </c>
-      <c r="O4" s="50">
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
         <v>5</v>
       </c>
-      <c r="P4" s="50">
+      <c r="P4">
         <v>2</v>
       </c>
-      <c r="Q4" s="50">
+      <c r="Q4">
         <v>10</v>
       </c>
-      <c r="R4" s="50">
-        <v>1</v>
-      </c>
-      <c r="S4" s="52" t="s">
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T4" s="50">
-        <v>1</v>
-      </c>
-      <c r="U4" s="50">
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
         <v>10</v>
       </c>
-      <c r="V4" s="50">
+      <c r="V4">
         <v>50</v>
       </c>
-      <c r="W4" s="50">
-        <v>1</v>
-      </c>
-      <c r="X4" s="50" t="s">
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4" t="s">
         <v>62</v>
       </c>
-      <c r="Y4" s="50" t="s">
+      <c r="Y4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="50">
+    <row r="5" spans="1:25">
+      <c r="A5">
         <v>1000002</v>
       </c>
-      <c r="B5" s="50">
-        <v>1</v>
-      </c>
-      <c r="C5" s="50">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
         <v>2</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="D5" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="50" t="s">
+      <c r="E5" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="50" t="s">
+      <c r="G5" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="50" t="s">
+      <c r="H5" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5">
         <v>20</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5">
         <v>60</v>
       </c>
-      <c r="K5" s="50">
-        <v>1</v>
-      </c>
-      <c r="L5" s="50" t="s">
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
         <v>68</v>
       </c>
-      <c r="M5" s="50" t="s">
+      <c r="M5" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="50" t="s">
+      <c r="N5" t="s">
         <v>69</v>
       </c>
-      <c r="O5" s="50" t="s">
+      <c r="O5" t="s">
         <v>70</v>
       </c>
-      <c r="P5" s="50">
+      <c r="P5">
         <v>3</v>
       </c>
-      <c r="Q5" s="53" t="s">
+      <c r="Q5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5">
         <v>2</v>
       </c>
-      <c r="S5" s="50" t="s">
+      <c r="S5" t="s">
         <v>72</v>
       </c>
-      <c r="T5" s="50">
-        <v>1</v>
-      </c>
-      <c r="U5" s="50">
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
         <v>20</v>
       </c>
-      <c r="V5" s="50">
+      <c r="V5">
         <v>100</v>
       </c>
-      <c r="W5" s="50">
+      <c r="W5">
         <v>2</v>
       </c>
-      <c r="X5" s="50" t="s">
+      <c r="X5" t="s">
         <v>73</v>
       </c>
-      <c r="Y5" s="50" t="s">
+      <c r="Y5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="50">
+    <row r="6" spans="1:25">
+      <c r="A6">
         <v>1000003</v>
       </c>
-      <c r="B6" s="50">
-        <v>1</v>
-      </c>
-      <c r="C6" s="50">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="50" t="s">
+      <c r="G6" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6">
         <v>3</v>
       </c>
-      <c r="I6" s="50" t="s">
+      <c r="I6" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="50">
+      <c r="J6">
         <v>60</v>
       </c>
-      <c r="K6" s="50">
-        <v>1</v>
-      </c>
-      <c r="L6" s="50" t="s">
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
         <v>78</v>
       </c>
-      <c r="M6" s="50" t="s">
+      <c r="M6" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="50" t="s">
+      <c r="N6" t="s">
         <v>79</v>
       </c>
-      <c r="O6" s="50" t="s">
+      <c r="O6" t="s">
         <v>80</v>
       </c>
-      <c r="P6" s="54" t="s">
+      <c r="P6" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="Q6" s="50" t="s">
+      <c r="Q6" t="s">
         <v>82</v>
       </c>
-      <c r="R6" s="50">
+      <c r="R6">
         <v>3</v>
       </c>
-      <c r="S6" s="50" t="s">
+      <c r="S6" t="s">
         <v>83</v>
       </c>
-      <c r="T6" s="50">
+      <c r="T6">
         <v>2</v>
       </c>
-      <c r="U6" s="50">
+      <c r="U6">
         <v>30</v>
       </c>
-      <c r="V6" s="50">
+      <c r="V6">
         <v>150</v>
       </c>
-      <c r="W6" s="50">
+      <c r="W6">
         <v>3</v>
       </c>
-      <c r="X6" s="50" t="s">
+      <c r="X6" t="s">
         <v>84</v>
       </c>
-      <c r="Y6" s="50" t="s">
+      <c r="Y6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="50">
+    <row r="7" spans="1:25">
+      <c r="A7">
         <v>1000004</v>
       </c>
-      <c r="B7" s="50">
-        <v>1</v>
-      </c>
-      <c r="C7" s="50">
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
         <v>4</v>
       </c>
-      <c r="D7" s="50" t="s">
+      <c r="D7" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="50" t="s">
+      <c r="E7" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="50" t="s">
+      <c r="G7" t="s">
         <v>87</v>
       </c>
-      <c r="H7" s="50">
+      <c r="H7">
         <v>4</v>
       </c>
-      <c r="I7" s="50" t="s">
+      <c r="I7" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="50">
+      <c r="J7">
         <v>60</v>
       </c>
-      <c r="K7" s="50">
-        <v>1</v>
-      </c>
-      <c r="L7" s="50" t="s">
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
         <v>89</v>
       </c>
-      <c r="M7" s="50" t="s">
+      <c r="M7" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="50" t="s">
+      <c r="N7" t="s">
         <v>90</v>
       </c>
-      <c r="O7" s="50" t="s">
+      <c r="O7" t="s">
         <v>91</v>
       </c>
-      <c r="P7" s="54" t="s">
+      <c r="P7" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="Q7" s="50" t="s">
+      <c r="Q7" t="s">
         <v>93</v>
       </c>
-      <c r="R7" s="50">
+      <c r="R7">
         <v>4</v>
       </c>
-      <c r="S7" s="50" t="s">
+      <c r="S7" t="s">
         <v>94</v>
       </c>
-      <c r="T7" s="50">
+      <c r="T7">
         <v>2</v>
       </c>
-      <c r="U7" s="50">
+      <c r="U7">
         <v>40</v>
       </c>
-      <c r="V7" s="50">
+      <c r="V7">
         <v>200</v>
       </c>
-      <c r="W7" s="50">
+      <c r="W7">
         <v>4</v>
       </c>
-      <c r="X7" s="50" t="s">
+      <c r="X7" t="s">
         <v>95</v>
       </c>
-      <c r="Y7" s="50" t="s">
+      <c r="Y7" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="50">
+    <row r="8" spans="1:25">
+      <c r="A8">
         <v>1000005</v>
       </c>
-      <c r="B8" s="50">
-        <v>1</v>
-      </c>
-      <c r="C8" s="50">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
         <v>5</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="D8" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="50" t="s">
+      <c r="G8" t="s">
         <v>98</v>
       </c>
-      <c r="H8" s="50">
+      <c r="H8">
         <v>5</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="50">
+      <c r="J8">
         <v>60</v>
       </c>
-      <c r="K8" s="50">
-        <v>1</v>
-      </c>
-      <c r="L8" s="50" t="s">
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
         <v>99</v>
       </c>
-      <c r="M8" s="50" t="s">
+      <c r="M8" t="s">
         <v>58</v>
       </c>
-      <c r="N8" s="50" t="s">
+      <c r="N8" t="s">
         <v>67</v>
       </c>
-      <c r="O8" s="50" t="s">
+      <c r="O8" t="s">
         <v>93</v>
       </c>
-      <c r="P8" s="54" t="s">
+      <c r="P8" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="Q8" s="50" t="s">
+      <c r="Q8" t="s">
         <v>101</v>
       </c>
-      <c r="R8" s="50">
+      <c r="R8">
         <v>5</v>
       </c>
-      <c r="S8" s="50" t="s">
+      <c r="S8" t="s">
         <v>102</v>
       </c>
-      <c r="T8" s="50">
+      <c r="T8">
         <v>2</v>
       </c>
-      <c r="U8" s="50">
+      <c r="U8">
         <v>50</v>
       </c>
-      <c r="V8" s="50">
+      <c r="V8">
         <v>250</v>
       </c>
-      <c r="W8" s="50">
+      <c r="W8">
         <v>5</v>
       </c>
-      <c r="X8" s="50" t="s">
+      <c r="X8" t="s">
         <v>103</v>
       </c>
-      <c r="Y8" s="50" t="s">
+      <c r="Y8" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="50">
+    <row r="9" spans="1:25">
+      <c r="A9">
         <v>1000006</v>
       </c>
-      <c r="B9" s="50">
-        <v>1</v>
-      </c>
-      <c r="C9" s="50">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
         <v>6</v>
       </c>
-      <c r="D9" s="50" t="s">
+      <c r="D9" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="E9" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="50" t="s">
+      <c r="G9" t="s">
         <v>106</v>
       </c>
-      <c r="H9" s="50">
+      <c r="H9">
         <v>6</v>
       </c>
-      <c r="I9" s="50" t="s">
+      <c r="I9" t="s">
         <v>107</v>
       </c>
-      <c r="J9" s="50">
+      <c r="J9">
         <v>60</v>
       </c>
-      <c r="K9" s="50">
-        <v>1</v>
-      </c>
-      <c r="L9" s="50" t="s">
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
         <v>108</v>
       </c>
-      <c r="M9" s="50" t="s">
+      <c r="M9" t="s">
         <v>58</v>
       </c>
-      <c r="N9" s="50" t="s">
+      <c r="N9" t="s">
         <v>109</v>
       </c>
-      <c r="O9" s="50" t="s">
+      <c r="O9" t="s">
         <v>110</v>
       </c>
-      <c r="P9" s="50" t="s">
+      <c r="P9" t="s">
         <v>100</v>
       </c>
-      <c r="Q9" s="50" t="s">
+      <c r="Q9" t="s">
         <v>111</v>
       </c>
-      <c r="R9" s="50">
+      <c r="R9">
         <v>6</v>
       </c>
-      <c r="S9" s="50" t="s">
+      <c r="S9" t="s">
         <v>112</v>
       </c>
-      <c r="T9" s="50">
+      <c r="T9">
         <v>3</v>
       </c>
-      <c r="U9" s="50">
+      <c r="U9">
         <v>60</v>
       </c>
-      <c r="V9" s="50">
+      <c r="V9">
         <v>300</v>
       </c>
-      <c r="W9" s="50">
+      <c r="W9">
         <v>6</v>
       </c>
-      <c r="X9" s="50" t="s">
+      <c r="X9" t="s">
         <v>113</v>
       </c>
-      <c r="Y9" s="50" t="s">
+      <c r="Y9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="50">
+    <row r="10" spans="1:25">
+      <c r="A10">
         <v>1000007</v>
       </c>
-      <c r="B10" s="50">
-        <v>1</v>
-      </c>
-      <c r="C10" s="50">
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>7</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="D10" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="50" t="s">
+      <c r="G10" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="50">
+      <c r="H10">
         <v>7</v>
       </c>
-      <c r="I10" s="50" t="s">
+      <c r="I10" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="50">
+      <c r="J10">
         <v>60</v>
       </c>
-      <c r="K10" s="50">
-        <v>1</v>
-      </c>
-      <c r="L10" s="50" t="s">
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
         <v>77</v>
       </c>
-      <c r="M10" s="50" t="s">
+      <c r="M10" t="s">
         <v>58</v>
       </c>
-      <c r="N10" s="50" t="s">
+      <c r="N10" t="s">
         <v>118</v>
       </c>
-      <c r="O10" s="50" t="s">
+      <c r="O10" t="s">
         <v>119</v>
       </c>
-      <c r="P10" s="50" t="s">
+      <c r="P10" t="s">
         <v>120</v>
       </c>
-      <c r="Q10" s="50" t="s">
+      <c r="Q10" t="s">
         <v>121</v>
       </c>
-      <c r="R10" s="50">
+      <c r="R10">
         <v>7</v>
       </c>
-      <c r="S10" s="50" t="s">
+      <c r="S10" t="s">
         <v>122</v>
       </c>
-      <c r="T10" s="50">
+      <c r="T10">
         <v>3</v>
       </c>
-      <c r="U10" s="50">
+      <c r="U10">
         <v>70</v>
       </c>
-      <c r="V10" s="50">
+      <c r="V10">
         <v>350</v>
       </c>
-      <c r="W10" s="50">
+      <c r="W10">
         <v>7</v>
       </c>
-      <c r="X10" s="50" t="s">
+      <c r="X10" t="s">
         <v>123</v>
       </c>
-      <c r="Y10" s="50" t="s">
+      <c r="Y10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="50">
+    <row r="11" spans="1:25">
+      <c r="A11">
         <v>1000008</v>
       </c>
-      <c r="B11" s="50">
-        <v>1</v>
-      </c>
-      <c r="C11" s="50">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
         <v>8</v>
       </c>
-      <c r="D11" s="50" t="s">
+      <c r="D11" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="50" t="s">
+      <c r="E11" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" t="s">
         <v>125</v>
       </c>
-      <c r="G11" s="50" t="s">
+      <c r="G11" t="s">
         <v>125</v>
       </c>
-      <c r="H11" s="50">
+      <c r="H11">
         <v>8</v>
       </c>
-      <c r="I11" s="50">
+      <c r="I11">
         <v>80</v>
       </c>
-      <c r="J11" s="50">
+      <c r="J11">
         <v>60</v>
       </c>
-      <c r="K11" s="50">
-        <v>1</v>
-      </c>
-      <c r="L11" s="50">
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
         <v>2</v>
       </c>
-      <c r="M11" s="50">
+      <c r="M11">
         <v>4.5</v>
       </c>
-      <c r="N11" s="50">
-        <v>1</v>
-      </c>
-      <c r="O11" s="50" t="s">
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="s">
         <v>126</v>
       </c>
-      <c r="P11" s="50" t="s">
+      <c r="P11" t="s">
         <v>120</v>
       </c>
-      <c r="Q11" s="50" t="s">
+      <c r="Q11" t="s">
         <v>127</v>
       </c>
-      <c r="R11" s="50">
+      <c r="R11">
         <v>8</v>
       </c>
-      <c r="S11" s="50" t="s">
+      <c r="S11" t="s">
         <v>128</v>
       </c>
-      <c r="T11" s="50">
+      <c r="T11">
         <v>3</v>
       </c>
-      <c r="U11" s="50">
+      <c r="U11">
         <v>80</v>
       </c>
-      <c r="V11" s="50">
+      <c r="V11">
         <v>400</v>
       </c>
-      <c r="W11" s="50">
+      <c r="W11">
         <v>8</v>
       </c>
-      <c r="X11" s="50" t="s">
+      <c r="X11" t="s">
         <v>129</v>
       </c>
-      <c r="Y11" s="50" t="s">
+      <c r="Y11" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="50">
+    <row r="12" spans="1:25">
+      <c r="A12">
         <v>1000009</v>
       </c>
-      <c r="B12" s="50">
-        <v>1</v>
-      </c>
-      <c r="C12" s="50">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
         <v>9</v>
       </c>
-      <c r="D12" s="50" t="s">
+      <c r="D12" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" t="s">
         <v>125</v>
       </c>
-      <c r="G12" s="50" t="s">
+      <c r="G12" t="s">
         <v>125</v>
       </c>
-      <c r="H12" s="50">
+      <c r="H12">
         <v>9</v>
       </c>
-      <c r="I12" s="50">
+      <c r="I12">
         <v>90</v>
       </c>
-      <c r="J12" s="50">
+      <c r="J12">
         <v>60</v>
       </c>
-      <c r="K12" s="50">
-        <v>1</v>
-      </c>
-      <c r="L12" s="50">
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
         <v>2</v>
       </c>
-      <c r="M12" s="50">
+      <c r="M12">
         <v>5</v>
       </c>
-      <c r="N12" s="50">
-        <v>1</v>
-      </c>
-      <c r="O12" s="50" t="s">
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="s">
         <v>131</v>
       </c>
-      <c r="P12" s="50" t="s">
+      <c r="P12" t="s">
         <v>120</v>
       </c>
-      <c r="Q12" s="50" t="s">
+      <c r="Q12" t="s">
         <v>132</v>
       </c>
-      <c r="R12" s="50">
+      <c r="R12">
         <v>9</v>
       </c>
-      <c r="S12" s="50" t="s">
+      <c r="S12" t="s">
         <v>133</v>
       </c>
-      <c r="T12" s="50">
+      <c r="T12">
         <v>4</v>
       </c>
-      <c r="U12" s="50">
+      <c r="U12">
         <v>90</v>
       </c>
-      <c r="V12" s="50">
+      <c r="V12">
         <v>450</v>
       </c>
-      <c r="W12" s="50">
+      <c r="W12">
         <v>9</v>
       </c>
-      <c r="X12" s="50" t="s">
+      <c r="X12" t="s">
         <v>134</v>
       </c>
-      <c r="Y12" s="50" t="s">
+      <c r="Y12" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="50">
+    <row r="13" spans="1:25">
+      <c r="A13">
         <v>1000010</v>
       </c>
-      <c r="B13" s="50">
-        <v>1</v>
-      </c>
-      <c r="C13" s="50">
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
         <v>10</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="D13" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E13" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" t="s">
         <v>125</v>
       </c>
-      <c r="G13" s="50" t="s">
+      <c r="G13" t="s">
         <v>125</v>
       </c>
-      <c r="H13" s="50">
+      <c r="H13">
         <v>10</v>
       </c>
-      <c r="I13" s="50">
+      <c r="I13">
         <v>100</v>
       </c>
-      <c r="J13" s="50">
+      <c r="J13">
         <v>60</v>
       </c>
-      <c r="K13" s="50">
-        <v>1</v>
-      </c>
-      <c r="L13" s="50">
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
         <v>2</v>
       </c>
-      <c r="M13" s="50">
+      <c r="M13">
         <v>5.5</v>
       </c>
-      <c r="N13" s="50">
-        <v>1</v>
-      </c>
-      <c r="O13" s="50" t="s">
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
         <v>136</v>
       </c>
-      <c r="P13" s="50" t="s">
+      <c r="P13" t="s">
         <v>120</v>
       </c>
-      <c r="Q13" s="50" t="s">
+      <c r="Q13" t="s">
         <v>137</v>
       </c>
-      <c r="R13" s="50">
+      <c r="R13">
         <v>10</v>
       </c>
-      <c r="S13" s="50" t="s">
+      <c r="S13" t="s">
         <v>138</v>
       </c>
-      <c r="T13" s="50">
+      <c r="T13">
         <v>4</v>
       </c>
-      <c r="U13" s="50">
+      <c r="U13">
         <v>100</v>
       </c>
-      <c r="V13" s="50">
+      <c r="V13">
         <v>500</v>
       </c>
-      <c r="W13" s="50">
+      <c r="W13">
         <v>10</v>
       </c>
-      <c r="X13" s="50" t="s">
+      <c r="X13" t="s">
         <v>139</v>
       </c>
-      <c r="Y13" s="50" t="s">
+      <c r="Y13" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="32" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="33" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="34" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="35" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="36" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="37" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="38" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="39" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="40" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="41" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="73" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="74" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="75" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="76" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="77" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="78" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="79" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="80" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="31" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="32" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="33" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="34" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="35" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="36" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="37" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="38" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="39" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="40" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="41" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="73" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="74" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="75" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="76" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="77" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="78" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="79" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="80" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="81" s="1" customFormat="1" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -1,19 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity\DemonLordRoguelike\Demon Lord Roguelike\Assets\Data\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="144">
   <si>
     <t>id</t>
   </si>
@@ -228,9 +247,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>9-10</t>
-  </si>
-  <si>
     <t>200-250</t>
   </si>
   <si>
@@ -261,9 +277,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>8-10</t>
-  </si>
-  <si>
     <t>300-350</t>
   </si>
   <si>
@@ -294,33 +307,30 @@
     <t>5</t>
   </si>
   <si>
+    <t>400-450</t>
+  </si>
+  <si>
+    <t>剑与魔法-难度4</t>
+  </si>
+  <si>
+    <t>#FBC02D</t>
+  </si>
+  <si>
+    <t>1040010001&amp;1010020002&amp;1020010001&amp;1030010001&amp;1030020001&amp;1030030001&amp;1030040001</t>
+  </si>
+  <si>
+    <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1020020001&amp;1020030001&amp;1031030001&amp;1031040001</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>7-10</t>
   </si>
   <si>
-    <t>400-450</t>
-  </si>
-  <si>
-    <t>剑与魔法-难度4</t>
-  </si>
-  <si>
-    <t>#FBC02D</t>
-  </si>
-  <si>
-    <t>1040010001&amp;1010020002&amp;1020010001&amp;1030010001&amp;1030020001&amp;1030030001&amp;1030040001</t>
-  </si>
-  <si>
-    <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1020020001&amp;1020030001&amp;1031030001&amp;1031040001</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>5-6</t>
   </si>
   <si>
-    <t>6-10</t>
-  </si>
-  <si>
     <t>500-550</t>
   </si>
   <si>
@@ -346,9 +356,6 @@
   </si>
   <si>
     <t>8-11</t>
-  </si>
-  <si>
-    <t>5-10</t>
   </si>
   <si>
     <t>600-650</t>
@@ -462,13 +469,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -476,6 +489,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -483,12 +497,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -496,6 +512,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -503,6 +520,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -510,6 +528,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -517,6 +536,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -524,12 +544,14 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -537,6 +559,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -544,6 +567,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -551,12 +575,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -564,30 +590,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1041,166 +1072,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1256,74 +1136,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1612,1056 +1429,1053 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Y13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:Y81"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="16" customWidth="1" style="51"/>
-    <col min="4" max="4" width="17.125" customWidth="1" style="51"/>
-    <col min="5" max="5" width="36.5" customWidth="1" style="51"/>
-    <col min="6" max="6" width="23.75" customWidth="1" style="51"/>
-    <col min="7" max="7" width="18.375" customWidth="1" style="51"/>
-    <col min="8" max="8" width="31.875" customWidth="1" style="51"/>
-    <col min="9" max="9" width="18.25" customWidth="1" style="51"/>
-    <col min="10" max="16" width="16" customWidth="1" style="51"/>
-    <col min="17" max="17" width="12.25" customWidth="1" style="51"/>
-    <col min="18" max="18" width="12.875" customWidth="1" style="51"/>
-    <col min="19" max="19" width="27.125" customWidth="1" style="51"/>
-    <col min="20" max="20" width="17.375" customWidth="1" style="51"/>
-    <col min="21" max="21" width="36.875" customWidth="1" style="51"/>
-    <col min="22" max="22" width="29.375" customWidth="1" style="51"/>
-    <col min="23" max="23" width="42.875" customWidth="1" style="51"/>
-    <col min="24" max="24" width="25.125" customWidth="1" style="51"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
+    <col min="10" max="16" width="16" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12.25" style="1" customWidth="1"/>
+    <col min="18" max="18" width="12.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="27.125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="17.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="36.875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="29.375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="42.875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="25.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="51" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="51" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="51" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="51" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="51" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="51" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="51" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="51" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="51" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="51" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="51" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="51" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="50" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="50" t="s">
+    <row r="2" spans="1:25">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="51" t="s">
+      <c r="F2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="51" t="s">
+      <c r="L2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="51" t="s">
+      <c r="M2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="51" t="s">
+      <c r="N2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="51" t="s">
+      <c r="O2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="51" t="s">
+      <c r="P2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="51" t="s">
+      <c r="Q2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="R2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="S2" s="51" t="s">
+      <c r="S2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="51" t="s">
+      <c r="T2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="51" t="s">
+      <c r="U2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="51" t="s">
+      <c r="V2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="51" t="s">
+      <c r="W2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="51" t="s">
+      <c r="X2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" s="50" t="s">
+      <c r="Y2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="50" t="s">
+    <row r="3" spans="1:25">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="51" t="s">
+      <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="51" t="s">
+      <c r="E3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="51" t="s">
+      <c r="F3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="51" t="s">
+      <c r="G3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="J3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="51" t="s">
+      <c r="L3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="51" t="s">
+      <c r="M3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="51" t="s">
+      <c r="N3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="51" t="s">
+      <c r="O3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="51" t="s">
+      <c r="P3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="51" t="s">
+      <c r="Q3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="51" t="s">
+      <c r="R3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="51" t="s">
+      <c r="S3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="T3" s="51" t="s">
+      <c r="T3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="51" t="s">
+      <c r="U3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="V3" s="51" t="s">
+      <c r="V3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="W3" s="51" t="s">
+      <c r="W3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="X3" s="51" t="s">
+      <c r="X3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="Y3" s="50" t="s">
+      <c r="Y3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="50">
+    <row r="4" spans="1:25">
+      <c r="A4">
         <v>1000001</v>
       </c>
-      <c r="B4" s="50">
-        <v>1</v>
-      </c>
-      <c r="C4" s="51">
-        <v>1</v>
-      </c>
-      <c r="D4" s="51" t="s">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="F4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="J4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="51">
-        <v>1</v>
-      </c>
-      <c r="L4" s="51" t="s">
+      <c r="K4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="51">
-        <v>1</v>
-      </c>
-      <c r="N4" s="51">
-        <v>1</v>
-      </c>
-      <c r="O4" s="51">
+      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1">
         <v>5</v>
       </c>
-      <c r="P4" s="51">
+      <c r="P4" s="1">
         <v>2</v>
       </c>
-      <c r="Q4" s="51">
+      <c r="Q4" s="1">
         <v>10</v>
       </c>
-      <c r="R4" s="51">
-        <v>1</v>
-      </c>
-      <c r="S4" s="52" t="s">
+      <c r="R4" s="1">
+        <v>1</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T4" s="51">
-        <v>1</v>
-      </c>
-      <c r="U4" s="51">
+      <c r="T4" s="1">
+        <v>1</v>
+      </c>
+      <c r="U4" s="1">
         <v>10</v>
       </c>
-      <c r="V4" s="51">
+      <c r="V4" s="1">
         <v>50</v>
       </c>
-      <c r="W4" s="51">
-        <v>1</v>
-      </c>
-      <c r="X4" s="51" t="s">
+      <c r="W4" s="1">
+        <v>1</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Y4" s="50" t="s">
+      <c r="Y4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="50">
+    <row r="5" spans="1:25">
+      <c r="A5">
         <v>1000002</v>
       </c>
-      <c r="B5" s="50">
-        <v>1</v>
-      </c>
-      <c r="C5" s="51">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
         <v>2</v>
       </c>
-      <c r="D5" s="51" t="s">
+      <c r="D5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="G5" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="1">
         <v>20</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="1">
         <v>60</v>
       </c>
-      <c r="K5" s="51">
-        <v>1</v>
-      </c>
-      <c r="L5" s="51" t="s">
+      <c r="K5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M5" s="51" t="s">
+      <c r="M5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="51" t="s">
+      <c r="N5" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="O5" s="51" t="s">
+      <c r="O5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="1">
         <v>3</v>
       </c>
-      <c r="Q5" s="53" t="s">
+      <c r="Q5" s="1">
+        <v>10</v>
+      </c>
+      <c r="R5" s="1">
+        <v>2</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="R5" s="51">
+      <c r="T5" s="1">
+        <v>1</v>
+      </c>
+      <c r="U5" s="1">
+        <v>20</v>
+      </c>
+      <c r="V5" s="1">
+        <v>100</v>
+      </c>
+      <c r="W5" s="1">
         <v>2</v>
       </c>
-      <c r="S5" s="51" t="s">
+      <c r="X5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="T5" s="51">
-        <v>1</v>
-      </c>
-      <c r="U5" s="51">
-        <v>20</v>
-      </c>
-      <c r="V5" s="51">
+      <c r="Y5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6">
+        <v>1000003</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="1">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" s="1">
+        <v>60</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>10</v>
+      </c>
+      <c r="R6" s="1">
+        <v>3</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="T6" s="1">
+        <v>2</v>
+      </c>
+      <c r="U6" s="1">
+        <v>30</v>
+      </c>
+      <c r="V6" s="1">
+        <v>150</v>
+      </c>
+      <c r="W6" s="1">
+        <v>3</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7">
+        <v>1000004</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="1">
+        <v>4</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="1">
+        <v>60</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>10</v>
+      </c>
+      <c r="R7" s="1">
+        <v>4</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="T7" s="1">
+        <v>2</v>
+      </c>
+      <c r="U7" s="1">
+        <v>40</v>
+      </c>
+      <c r="V7" s="1">
+        <v>200</v>
+      </c>
+      <c r="W7" s="1">
+        <v>4</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8">
+        <v>1000005</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="1">
+        <v>5</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" s="1">
+        <v>60</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>10</v>
+      </c>
+      <c r="R8" s="1">
+        <v>5</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T8" s="1">
+        <v>2</v>
+      </c>
+      <c r="U8" s="1">
+        <v>50</v>
+      </c>
+      <c r="V8" s="1">
+        <v>250</v>
+      </c>
+      <c r="W8" s="1">
+        <v>5</v>
+      </c>
+      <c r="X8" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="W5" s="51">
-        <v>2</v>
-      </c>
-      <c r="X5" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="Y5" s="50" t="s">
-        <v>74</v>
+      <c r="Y8" t="s">
+        <v>101</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="50">
-        <v>1000003</v>
-      </c>
-      <c r="B6" s="50">
-        <v>1</v>
-      </c>
-      <c r="C6" s="51">
+    <row r="9" spans="1:25">
+      <c r="A9">
+        <v>1000006</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="1">
+        <v>6</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="1">
+        <v>60</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>10</v>
+      </c>
+      <c r="R9" s="1">
+        <v>6</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="T9" s="1">
         <v>3</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="U9" s="1">
+        <v>60</v>
+      </c>
+      <c r="V9" s="1">
+        <v>300</v>
+      </c>
+      <c r="W9" s="1">
+        <v>6</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
+      <c r="A10">
+        <v>1000007</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="51" t="s">
+      <c r="F10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" s="1">
+        <v>7</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="1">
+        <v>60</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="51">
+      <c r="M10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>10</v>
+      </c>
+      <c r="R10" s="1">
+        <v>7</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="T10" s="1">
         <v>3</v>
       </c>
-      <c r="I6" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="J6" s="51">
+      <c r="U10" s="1">
+        <v>70</v>
+      </c>
+      <c r="V10" s="1">
+        <v>350</v>
+      </c>
+      <c r="W10" s="1">
+        <v>7</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
+      <c r="A11">
+        <v>1000008</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H11" s="1">
+        <v>8</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J11" s="1">
         <v>60</v>
       </c>
-      <c r="K6" s="51">
-        <v>1</v>
-      </c>
-      <c r="L6" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="M6" s="51" t="s">
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="O6" s="51" t="s">
+      <c r="N11" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>10</v>
+      </c>
+      <c r="R11" s="1">
+        <v>8</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="T11" s="1">
+        <v>3</v>
+      </c>
+      <c r="U11" s="1">
         <v>80</v>
       </c>
-      <c r="P6" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q6" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="R6" s="51">
-        <v>3</v>
-      </c>
-      <c r="S6" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="T6" s="51">
-        <v>2</v>
-      </c>
-      <c r="U6" s="51">
-        <v>30</v>
-      </c>
-      <c r="V6" s="51">
-        <v>150</v>
-      </c>
-      <c r="W6" s="51">
-        <v>3</v>
-      </c>
-      <c r="X6" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y6" s="50" t="s">
-        <v>85</v>
+      <c r="V11" s="1">
+        <v>400</v>
+      </c>
+      <c r="W11" s="1">
+        <v>8</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="50">
-        <v>1000004</v>
-      </c>
-      <c r="B7" s="50">
-        <v>1</v>
-      </c>
-      <c r="C7" s="51">
+    <row r="12" spans="1:25">
+      <c r="A12">
+        <v>1000009</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H12" s="1">
+        <v>9</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J12" s="1">
+        <v>60</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>10</v>
+      </c>
+      <c r="R12" s="1">
+        <v>9</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="T12" s="1">
         <v>4</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="U12" s="1">
+        <v>90</v>
+      </c>
+      <c r="V12" s="1">
+        <v>450</v>
+      </c>
+      <c r="W12" s="1">
+        <v>9</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
+      <c r="A13">
+        <v>1000010</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="G7" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="H7" s="51">
+      <c r="F13" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13" s="1">
+        <v>10</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J13" s="1">
+        <v>60</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>10</v>
+      </c>
+      <c r="R13" s="1">
+        <v>10</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="T13" s="1">
         <v>4</v>
       </c>
-      <c r="I7" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="J7" s="51">
-        <v>60</v>
-      </c>
-      <c r="K7" s="51">
-        <v>1</v>
-      </c>
-      <c r="L7" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="M7" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="O7" s="51" t="s">
-        <v>91</v>
-      </c>
-      <c r="P7" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q7" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="R7" s="51">
-        <v>4</v>
-      </c>
-      <c r="S7" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="T7" s="51">
-        <v>2</v>
-      </c>
-      <c r="U7" s="51">
-        <v>40</v>
-      </c>
-      <c r="V7" s="51">
-        <v>200</v>
-      </c>
-      <c r="W7" s="51">
-        <v>4</v>
-      </c>
-      <c r="X7" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y7" s="50" t="s">
-        <v>96</v>
+      <c r="U13" s="1">
+        <v>100</v>
+      </c>
+      <c r="V13" s="1">
+        <v>500</v>
+      </c>
+      <c r="W13" s="1">
+        <v>10</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>143</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="50">
-        <v>1000005</v>
-      </c>
-      <c r="B8" s="50">
-        <v>1</v>
-      </c>
-      <c r="C8" s="51">
-        <v>5</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="H8" s="51">
-        <v>5</v>
-      </c>
-      <c r="I8" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="J8" s="51">
-        <v>60</v>
-      </c>
-      <c r="K8" s="51">
-        <v>1</v>
-      </c>
-      <c r="L8" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="M8" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="O8" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="P8" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q8" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="R8" s="51">
-        <v>5</v>
-      </c>
-      <c r="S8" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="T8" s="51">
-        <v>2</v>
-      </c>
-      <c r="U8" s="51">
-        <v>50</v>
-      </c>
-      <c r="V8" s="51">
-        <v>250</v>
-      </c>
-      <c r="W8" s="51">
-        <v>5</v>
-      </c>
-      <c r="X8" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y8" s="50" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="50">
-        <v>1000006</v>
-      </c>
-      <c r="B9" s="50">
-        <v>1</v>
-      </c>
-      <c r="C9" s="51">
-        <v>6</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="G9" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="H9" s="51">
-        <v>6</v>
-      </c>
-      <c r="I9" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="J9" s="51">
-        <v>60</v>
-      </c>
-      <c r="K9" s="51">
-        <v>1</v>
-      </c>
-      <c r="L9" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="M9" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="O9" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="P9" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q9" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="R9" s="51">
-        <v>6</v>
-      </c>
-      <c r="S9" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="T9" s="51">
-        <v>3</v>
-      </c>
-      <c r="U9" s="51">
-        <v>60</v>
-      </c>
-      <c r="V9" s="51">
-        <v>300</v>
-      </c>
-      <c r="W9" s="51">
-        <v>6</v>
-      </c>
-      <c r="X9" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y9" s="50" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="50">
-        <v>1000007</v>
-      </c>
-      <c r="B10" s="50">
-        <v>1</v>
-      </c>
-      <c r="C10" s="51">
-        <v>7</v>
-      </c>
-      <c r="D10" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="G10" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="H10" s="51">
-        <v>7</v>
-      </c>
-      <c r="I10" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="J10" s="51">
-        <v>60</v>
-      </c>
-      <c r="K10" s="51">
-        <v>1</v>
-      </c>
-      <c r="L10" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="M10" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N10" s="51" t="s">
-        <v>118</v>
-      </c>
-      <c r="O10" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="P10" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q10" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="R10" s="51">
-        <v>7</v>
-      </c>
-      <c r="S10" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="T10" s="51">
-        <v>3</v>
-      </c>
-      <c r="U10" s="51">
-        <v>70</v>
-      </c>
-      <c r="V10" s="51">
-        <v>350</v>
-      </c>
-      <c r="W10" s="51">
-        <v>7</v>
-      </c>
-      <c r="X10" s="51" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y10" s="50" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="50">
-        <v>1000008</v>
-      </c>
-      <c r="B11" s="50">
-        <v>1</v>
-      </c>
-      <c r="C11" s="51">
-        <v>8</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="G11" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="H11" s="51">
-        <v>8</v>
-      </c>
-      <c r="I11" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="J11" s="51">
-        <v>60</v>
-      </c>
-      <c r="K11" s="51">
-        <v>1</v>
-      </c>
-      <c r="L11" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="M11" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N11" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="O11" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="P11" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q11" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="R11" s="51">
-        <v>8</v>
-      </c>
-      <c r="S11" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="T11" s="51">
-        <v>3</v>
-      </c>
-      <c r="U11" s="51">
-        <v>80</v>
-      </c>
-      <c r="V11" s="51">
-        <v>400</v>
-      </c>
-      <c r="W11" s="51">
-        <v>8</v>
-      </c>
-      <c r="X11" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="Y11" s="50" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="50">
-        <v>1000009</v>
-      </c>
-      <c r="B12" s="50">
-        <v>1</v>
-      </c>
-      <c r="C12" s="51">
-        <v>9</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="H12" s="51">
-        <v>9</v>
-      </c>
-      <c r="I12" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="J12" s="51">
-        <v>60</v>
-      </c>
-      <c r="K12" s="51">
-        <v>1</v>
-      </c>
-      <c r="L12" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N12" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="O12" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="P12" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q12" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="R12" s="51">
-        <v>9</v>
-      </c>
-      <c r="S12" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="T12" s="51">
-        <v>4</v>
-      </c>
-      <c r="U12" s="51">
-        <v>90</v>
-      </c>
-      <c r="V12" s="51">
-        <v>450</v>
-      </c>
-      <c r="W12" s="51">
-        <v>9</v>
-      </c>
-      <c r="X12" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y12" s="50" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="50">
-        <v>1000010</v>
-      </c>
-      <c r="B13" s="50">
-        <v>1</v>
-      </c>
-      <c r="C13" s="51">
-        <v>10</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="H13" s="51">
-        <v>10</v>
-      </c>
-      <c r="I13" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="J13" s="51">
-        <v>60</v>
-      </c>
-      <c r="K13" s="51">
-        <v>1</v>
-      </c>
-      <c r="L13" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="M13" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="O13" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="P13" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q13" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="R13" s="51">
-        <v>10</v>
-      </c>
-      <c r="S13" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="T13" s="51">
-        <v>4</v>
-      </c>
-      <c r="U13" s="51">
-        <v>100</v>
-      </c>
-      <c r="V13" s="51">
-        <v>500</v>
-      </c>
-      <c r="W13" s="51">
-        <v>10</v>
-      </c>
-      <c r="X13" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="Y13" s="50" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="32" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="33" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="34" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="35" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="36" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="37" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="38" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="39" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="40" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="41" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="73" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="74" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="75" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="76" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="77" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="78" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="79" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="80" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="31" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="32" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="33" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="34" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="35" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="36" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="37" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="38" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="39" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="40" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="41" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="73" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="74" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="75" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="76" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="77" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="78" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="79" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="80" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="81" s="1" customFormat="1" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t>id</t>
   </si>
@@ -271,7 +271,7 @@
     <t>1.5</t>
   </si>
   <si>
-    <t>6-7</t>
+    <t>7</t>
   </si>
   <si>
     <t>4</t>
@@ -301,7 +301,7 @@
     <t>1.75</t>
   </si>
   <si>
-    <t>6-9</t>
+    <t>8</t>
   </si>
   <si>
     <t>5</t>
@@ -325,7 +325,7 @@
     <t>30</t>
   </si>
   <si>
-    <t>7-10</t>
+    <t>9</t>
   </si>
   <si>
     <t>5-6</t>
@@ -355,9 +355,6 @@
     <t>2.5</t>
   </si>
   <si>
-    <t>8-11</t>
-  </si>
-  <si>
     <t>600-650</t>
   </si>
   <si>
@@ -379,7 +376,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>9-12</t>
+    <t>11</t>
   </si>
   <si>
     <t>1-6</t>
@@ -406,7 +403,7 @@
     <t>3.5</t>
   </si>
   <si>
-    <t>9-13</t>
+    <t>12</t>
   </si>
   <si>
     <t>800-850</t>
@@ -427,7 +424,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>10-14</t>
+    <t>13</t>
   </si>
   <si>
     <t>900-950</t>
@@ -454,7 +451,7 @@
     <t>4.5</t>
   </si>
   <si>
-    <t>10-15</t>
+    <t>14</t>
   </si>
   <si>
     <t>1000-1200</t>
@@ -481,7 +478,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -489,7 +485,6 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -497,14 +492,12 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -512,7 +505,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -520,7 +512,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -528,7 +519,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -536,7 +526,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -544,14 +533,12 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -559,7 +546,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -567,7 +553,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -575,14 +560,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -590,35 +573,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1072,15 +1050,165 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+  <cellXfs count="54">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="3" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1431,1048 +1559,1048 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y81"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="16" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="31.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.25" style="1" customWidth="1"/>
-    <col min="10" max="16" width="16" style="1" customWidth="1"/>
-    <col min="17" max="17" width="12.25" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="27.125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="17.375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="36.875" style="1" customWidth="1"/>
-    <col min="22" max="22" width="29.375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="42.875" style="1" customWidth="1"/>
-    <col min="24" max="24" width="25.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1" style="51"/>
+    <col min="4" max="4" width="17.125" customWidth="1" style="51"/>
+    <col min="5" max="5" width="36.5" customWidth="1" style="51"/>
+    <col min="6" max="6" width="23.75" customWidth="1" style="51"/>
+    <col min="7" max="7" width="18.375" customWidth="1" style="51"/>
+    <col min="8" max="8" width="31.875" customWidth="1" style="51"/>
+    <col min="9" max="9" width="18.25" customWidth="1" style="51"/>
+    <col min="10" max="16" width="16" customWidth="1" style="51"/>
+    <col min="17" max="17" width="12.25" customWidth="1" style="51"/>
+    <col min="18" max="18" width="12.875" customWidth="1" style="51"/>
+    <col min="19" max="19" width="27.125" customWidth="1" style="51"/>
+    <col min="20" max="20" width="17.375" customWidth="1" style="51"/>
+    <col min="21" max="21" width="36.875" customWidth="1" style="51"/>
+    <col min="22" max="22" width="29.375" customWidth="1" style="51"/>
+    <col min="23" max="23" width="42.875" customWidth="1" style="51"/>
+    <col min="24" max="24" width="25.125" customWidth="1" style="51"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="50" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" s="50" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="Q3" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="S3" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="T3" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="U3" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="V3" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="W3" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="X3" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Y3" s="50" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="50">
         <v>1000001</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="B4" s="50">
+        <v>1</v>
+      </c>
+      <c r="C4" s="51">
+        <v>1</v>
+      </c>
+      <c r="D4" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="1">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1" t="s">
+      <c r="K4" s="51">
+        <v>1</v>
+      </c>
+      <c r="L4" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1</v>
-      </c>
-      <c r="O4" s="1">
+      <c r="M4" s="51">
+        <v>1</v>
+      </c>
+      <c r="N4" s="51">
+        <v>1</v>
+      </c>
+      <c r="O4" s="51">
         <v>5</v>
       </c>
-      <c r="P4" s="1">
+      <c r="P4" s="51">
         <v>2</v>
       </c>
-      <c r="Q4" s="1">
+      <c r="Q4" s="51">
         <v>10</v>
       </c>
-      <c r="R4" s="1">
-        <v>1</v>
-      </c>
-      <c r="S4" s="2" t="s">
+      <c r="R4" s="51">
+        <v>1</v>
+      </c>
+      <c r="S4" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="T4" s="1">
-        <v>1</v>
-      </c>
-      <c r="U4" s="1">
+      <c r="T4" s="51">
+        <v>1</v>
+      </c>
+      <c r="U4" s="51">
         <v>10</v>
       </c>
-      <c r="V4" s="1">
+      <c r="V4" s="51">
         <v>50</v>
       </c>
-      <c r="W4" s="1">
-        <v>1</v>
-      </c>
-      <c r="X4" s="1" t="s">
+      <c r="W4" s="51">
+        <v>1</v>
+      </c>
+      <c r="X4" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Y4" s="50" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" s="50">
         <v>1000002</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B5" s="50">
+        <v>1</v>
+      </c>
+      <c r="C5" s="51">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="51">
         <v>20</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="51">
         <v>60</v>
       </c>
-      <c r="K5" s="1">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1" t="s">
+      <c r="K5" s="51">
+        <v>1</v>
+      </c>
+      <c r="L5" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="51">
         <v>3</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="51">
         <v>10</v>
       </c>
-      <c r="R5" s="1">
+      <c r="R5" s="51">
         <v>2</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="S5" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="T5" s="1">
-        <v>1</v>
-      </c>
-      <c r="U5" s="1">
+      <c r="T5" s="51">
+        <v>1</v>
+      </c>
+      <c r="U5" s="51">
         <v>20</v>
       </c>
-      <c r="V5" s="1">
+      <c r="V5" s="51">
         <v>100</v>
       </c>
-      <c r="W5" s="1">
+      <c r="W5" s="51">
         <v>2</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="X5" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Y5" s="50" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" s="50">
         <v>1000003</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="B6" s="50">
+        <v>1</v>
+      </c>
+      <c r="C6" s="51">
         <v>3</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="51">
         <v>3</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="51">
         <v>60</v>
       </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1" t="s">
+      <c r="K6" s="51">
+        <v>1</v>
+      </c>
+      <c r="L6" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N6" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="O6" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="P6" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="51">
         <v>10</v>
       </c>
-      <c r="R6" s="1">
+      <c r="R6" s="51">
         <v>3</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="S6" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="T6" s="1">
+      <c r="T6" s="51">
         <v>2</v>
       </c>
-      <c r="U6" s="1">
+      <c r="U6" s="51">
         <v>30</v>
       </c>
-      <c r="V6" s="1">
+      <c r="V6" s="51">
         <v>150</v>
       </c>
-      <c r="W6" s="1">
+      <c r="W6" s="51">
         <v>3</v>
       </c>
-      <c r="X6" s="1" t="s">
+      <c r="X6" s="51" t="s">
         <v>82</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Y6" s="50" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" s="50">
         <v>1000004</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="B7" s="50">
+        <v>1</v>
+      </c>
+      <c r="C7" s="51">
         <v>4</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="51" t="s">
         <v>85</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="51">
         <v>4</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="51">
         <v>60</v>
       </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="s">
+      <c r="K7" s="51">
+        <v>1</v>
+      </c>
+      <c r="L7" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N7" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="O7" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="P7" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="51">
         <v>10</v>
       </c>
-      <c r="R7" s="1">
+      <c r="R7" s="51">
         <v>4</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="S7" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="T7" s="1">
+      <c r="T7" s="51">
         <v>2</v>
       </c>
-      <c r="U7" s="1">
+      <c r="U7" s="51">
         <v>40</v>
       </c>
-      <c r="V7" s="1">
+      <c r="V7" s="51">
         <v>200</v>
       </c>
-      <c r="W7" s="1">
+      <c r="W7" s="51">
         <v>4</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="X7" s="51" t="s">
         <v>92</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Y7" s="50" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" s="50">
         <v>1000005</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="B8" s="50">
+        <v>1</v>
+      </c>
+      <c r="C8" s="51">
         <v>5</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="51">
         <v>5</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="51" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="51">
         <v>60</v>
       </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
-      <c r="L8" s="1" t="s">
+      <c r="K8" s="51">
+        <v>1</v>
+      </c>
+      <c r="L8" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="O8" s="51" t="s">
         <v>97</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="P8" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="51">
         <v>10</v>
       </c>
-      <c r="R8" s="1">
+      <c r="R8" s="51">
         <v>5</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="S8" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="T8" s="1">
+      <c r="T8" s="51">
         <v>2</v>
       </c>
-      <c r="U8" s="1">
+      <c r="U8" s="51">
         <v>50</v>
       </c>
-      <c r="V8" s="1">
+      <c r="V8" s="51">
         <v>250</v>
       </c>
-      <c r="W8" s="1">
+      <c r="W8" s="51">
         <v>5</v>
       </c>
-      <c r="X8" s="1" t="s">
+      <c r="X8" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="Y8" s="50" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" s="50">
         <v>1000006</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="B9" s="50">
+        <v>1</v>
+      </c>
+      <c r="C9" s="51">
         <v>6</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="51">
         <v>6</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="51">
         <v>60</v>
       </c>
-      <c r="K9" s="1">
-        <v>1</v>
-      </c>
-      <c r="L9" s="1" t="s">
+      <c r="K9" s="51">
+        <v>1</v>
+      </c>
+      <c r="L9" s="51" t="s">
         <v>105</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="O9" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="P9" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q9" s="51">
+        <v>10</v>
+      </c>
+      <c r="R9" s="51">
+        <v>6</v>
+      </c>
+      <c r="S9" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q9" s="1">
+      <c r="T9" s="51">
+        <v>3</v>
+      </c>
+      <c r="U9" s="51">
+        <v>60</v>
+      </c>
+      <c r="V9" s="51">
+        <v>300</v>
+      </c>
+      <c r="W9" s="51">
+        <v>6</v>
+      </c>
+      <c r="X9" s="51" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y9" s="50" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="50">
+        <v>1000007</v>
+      </c>
+      <c r="B10" s="50">
+        <v>1</v>
+      </c>
+      <c r="C10" s="51">
+        <v>7</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="51">
+        <v>7</v>
+      </c>
+      <c r="I10" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="J10" s="51">
+        <v>60</v>
+      </c>
+      <c r="K10" s="51">
+        <v>1</v>
+      </c>
+      <c r="L10" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="O10" s="51" t="s">
+        <v>114</v>
+      </c>
+      <c r="P10" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q10" s="51">
         <v>10</v>
       </c>
-      <c r="R9" s="1">
-        <v>6</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="T9" s="1">
+      <c r="R10" s="51">
+        <v>7</v>
+      </c>
+      <c r="S10" s="51" t="s">
+        <v>116</v>
+      </c>
+      <c r="T10" s="51">
         <v>3</v>
       </c>
-      <c r="U9" s="1">
+      <c r="U10" s="51">
+        <v>70</v>
+      </c>
+      <c r="V10" s="51">
+        <v>350</v>
+      </c>
+      <c r="W10" s="51">
+        <v>7</v>
+      </c>
+      <c r="X10" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y10" s="50" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="50">
+        <v>1000008</v>
+      </c>
+      <c r="B11" s="50">
+        <v>1</v>
+      </c>
+      <c r="C11" s="51">
+        <v>8</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="H11" s="51">
+        <v>8</v>
+      </c>
+      <c r="I11" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="J11" s="51">
         <v>60</v>
       </c>
-      <c r="V9" s="1">
-        <v>300</v>
-      </c>
-      <c r="W9" s="1">
-        <v>6</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>110</v>
+      <c r="K11" s="51">
+        <v>1</v>
+      </c>
+      <c r="L11" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="M11" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="O11" s="51" t="s">
+        <v>123</v>
+      </c>
+      <c r="P11" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q11" s="51">
+        <v>10</v>
+      </c>
+      <c r="R11" s="51">
+        <v>8</v>
+      </c>
+      <c r="S11" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="T11" s="51">
+        <v>3</v>
+      </c>
+      <c r="U11" s="51">
+        <v>80</v>
+      </c>
+      <c r="V11" s="51">
+        <v>400</v>
+      </c>
+      <c r="W11" s="51">
+        <v>8</v>
+      </c>
+      <c r="X11" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y11" s="50" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
-      <c r="A10">
-        <v>1000007</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1">
-        <v>7</v>
-      </c>
-      <c r="D10" s="1" t="s">
+    <row r="12">
+      <c r="A12" s="50">
+        <v>1000009</v>
+      </c>
+      <c r="B12" s="50">
+        <v>1</v>
+      </c>
+      <c r="C12" s="51">
+        <v>9</v>
+      </c>
+      <c r="D12" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E12" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H10" s="1">
-        <v>7</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="F12" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="51">
+        <v>9</v>
+      </c>
+      <c r="I12" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="J12" s="51">
         <v>60</v>
       </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M10" s="1" t="s">
+      <c r="K12" s="51">
+        <v>1</v>
+      </c>
+      <c r="L12" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="O10" s="1" t="s">
+      <c r="N12" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="O12" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="P12" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="P10" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q10" s="1">
+      <c r="Q12" s="51">
         <v>10</v>
       </c>
-      <c r="R10" s="1">
-        <v>7</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="T10" s="1">
-        <v>3</v>
-      </c>
-      <c r="U10" s="1">
-        <v>70</v>
-      </c>
-      <c r="V10" s="1">
-        <v>350</v>
-      </c>
-      <c r="W10" s="1">
-        <v>7</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>119</v>
+      <c r="R12" s="51">
+        <v>9</v>
+      </c>
+      <c r="S12" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="T12" s="51">
+        <v>4</v>
+      </c>
+      <c r="U12" s="51">
+        <v>90</v>
+      </c>
+      <c r="V12" s="51">
+        <v>450</v>
+      </c>
+      <c r="W12" s="51">
+        <v>9</v>
+      </c>
+      <c r="X12" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y12" s="50" t="s">
+        <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
-      <c r="A11">
-        <v>1000008</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1" t="s">
+    <row r="13">
+      <c r="A13" s="50">
+        <v>1000010</v>
+      </c>
+      <c r="B13" s="50">
+        <v>1</v>
+      </c>
+      <c r="C13" s="51">
+        <v>10</v>
+      </c>
+      <c r="D13" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E13" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="H11" s="1">
-        <v>8</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="F13" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="H13" s="51">
+        <v>10</v>
+      </c>
+      <c r="I13" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="J13" s="51">
         <v>60</v>
       </c>
-      <c r="K11" s="1">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="M11" s="1" t="s">
+      <c r="K13" s="51">
+        <v>1</v>
+      </c>
+      <c r="L13" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="M13" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q11" s="1">
+      <c r="N13" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="O13" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="P13" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q13" s="51">
         <v>10</v>
       </c>
-      <c r="R11" s="1">
-        <v>8</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="T11" s="1">
-        <v>3</v>
-      </c>
-      <c r="U11" s="1">
-        <v>80</v>
-      </c>
-      <c r="V11" s="1">
-        <v>400</v>
-      </c>
-      <c r="W11" s="1">
-        <v>8</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>127</v>
+      <c r="R13" s="51">
+        <v>10</v>
+      </c>
+      <c r="S13" s="51" t="s">
+        <v>140</v>
+      </c>
+      <c r="T13" s="51">
+        <v>4</v>
+      </c>
+      <c r="U13" s="51">
+        <v>100</v>
+      </c>
+      <c r="V13" s="51">
+        <v>500</v>
+      </c>
+      <c r="W13" s="51">
+        <v>10</v>
+      </c>
+      <c r="X13" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y13" s="50" t="s">
+        <v>142</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
-      <c r="A12">
-        <v>1000009</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1">
-        <v>9</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" s="1">
-        <v>9</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J12" s="1">
-        <v>60</v>
-      </c>
-      <c r="K12" s="1">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>10</v>
-      </c>
-      <c r="R12" s="1">
-        <v>9</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="T12" s="1">
-        <v>4</v>
-      </c>
-      <c r="U12" s="1">
-        <v>90</v>
-      </c>
-      <c r="V12" s="1">
-        <v>450</v>
-      </c>
-      <c r="W12" s="1">
-        <v>9</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
-      <c r="A13">
-        <v>1000010</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H13" s="1">
-        <v>10</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J13" s="1">
-        <v>60</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>10</v>
-      </c>
-      <c r="R13" s="1">
-        <v>10</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="T13" s="1">
-        <v>4</v>
-      </c>
-      <c r="U13" s="1">
-        <v>100</v>
-      </c>
-      <c r="V13" s="1">
-        <v>500</v>
-      </c>
-      <c r="W13" s="1">
-        <v>10</v>
-      </c>
-      <c r="X13" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="32" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="33" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="34" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="35" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="36" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="37" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="38" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="39" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="40" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="41" s="1" customFormat="1" ht="15" customHeight="1"/>
-    <row r="73" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="74" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="75" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="76" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="77" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="78" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="79" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="80" s="1" customFormat="1" ht="12" customHeight="1"/>
-    <row r="81" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="32" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="33" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="34" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="35" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="36" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="37" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="38" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="39" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="40" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="41" ht="15" customHeight="1" s="51" customFormat="1"/>
+    <row r="73" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="74" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="75" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="76" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="77" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="78" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="79" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="80" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="FightTypeConquerInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="148">
   <si>
     <t>id</t>
   </si>
@@ -55,6 +55,12 @@
     <t>enemy_boss_ids</t>
   </si>
   <si>
+    <t>enemy_type_num</t>
+  </si>
+  <si>
+    <t>enemy_boss_type_num</t>
+  </si>
+  <si>
     <t>attack_boss_num</t>
   </si>
   <si>
@@ -142,6 +148,12 @@
     <t>boss列表（npcInfoId用&amp;分割）</t>
   </si>
   <si>
+    <t>普通敌人种类数量(单个数x或范围x-y; 留空=每次出怪从整池全随机)</t>
+  </si>
+  <si>
+    <t>boss种类数量(单个数x或范围x-y; 留空=每次出怪从整池全随机)</t>
+  </si>
+  <si>
     <t>boss数量(单个数x或范围x-y)</t>
   </si>
   <si>
@@ -208,6 +220,9 @@
     <t>1010020001</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -292,6 +307,9 @@
     <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1020020001&amp;1020030001</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>50</t>
   </si>
   <si>
@@ -302,9 +320,6 @@
   </si>
   <si>
     <t>8</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
   <si>
     <t>400-450</t>
@@ -478,6 +493,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -485,6 +501,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -492,12 +509,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -505,6 +524,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -512,6 +532,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -519,6 +540,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -526,6 +548,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -533,12 +556,14 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -546,6 +571,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -553,6 +579,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -560,12 +587,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -573,30 +602,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1050,165 +1084,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="3" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1559,1048 +1443,1104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:AA81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="16" customWidth="1" style="51"/>
-    <col min="4" max="4" width="17.125" customWidth="1" style="51"/>
-    <col min="5" max="5" width="36.5" customWidth="1" style="51"/>
-    <col min="6" max="6" width="23.75" customWidth="1" style="51"/>
-    <col min="7" max="7" width="18.375" customWidth="1" style="51"/>
-    <col min="8" max="8" width="31.875" customWidth="1" style="51"/>
-    <col min="9" max="9" width="18.25" customWidth="1" style="51"/>
-    <col min="10" max="16" width="16" customWidth="1" style="51"/>
-    <col min="17" max="17" width="12.25" customWidth="1" style="51"/>
-    <col min="18" max="18" width="12.875" customWidth="1" style="51"/>
-    <col min="19" max="19" width="27.125" customWidth="1" style="51"/>
-    <col min="20" max="20" width="17.375" customWidth="1" style="51"/>
-    <col min="21" max="21" width="36.875" customWidth="1" style="51"/>
-    <col min="22" max="22" width="29.375" customWidth="1" style="51"/>
-    <col min="23" max="23" width="42.875" customWidth="1" style="51"/>
-    <col min="24" max="24" width="25.125" customWidth="1" style="51"/>
+    <col min="1" max="2" width="13" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="109.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="69.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.25" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16" style="1" customWidth="1"/>
+    <col min="13" max="18" width="13" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.25" style="1" customWidth="1"/>
+    <col min="20" max="20" width="12.875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="27.125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="17.375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="36.875" style="1" customWidth="1"/>
+    <col min="24" max="24" width="29.375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="42.875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="25.125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:27">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="51" t="s">
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="51" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="51" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="51" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="51" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="51" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="51" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="51" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="51" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="51" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="51" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="51" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="51" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="51" t="s">
+      <c r="X1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="50" t="s">
+      <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2">
-      <c r="A2" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="51" t="s">
+    <row r="2" spans="1:27">
+      <c r="A2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="B2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="51" t="s">
+      <c r="C2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="D2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="51" t="s">
+      <c r="L2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="51" t="s">
+      <c r="O2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="U2" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="V2" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="W2" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="X2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y2" s="50" t="s">
-        <v>27</v>
+      <c r="U2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="50" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="50" t="s">
+    <row r="3" spans="1:27">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4">
+        <v>1000001</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>5</v>
+      </c>
+      <c r="R4" s="1">
+        <v>2</v>
+      </c>
+      <c r="S4" s="1">
+        <v>10</v>
+      </c>
+      <c r="T4" s="1">
+        <v>1</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="V4" s="1">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1">
+        <v>10</v>
+      </c>
+      <c r="X4" s="1">
+        <v>50</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
+      <c r="A5">
+        <v>1000002</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="1">
+        <v>20</v>
+      </c>
+      <c r="L5" s="1">
+        <v>60</v>
+      </c>
+      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="1">
+        <v>3</v>
+      </c>
+      <c r="S5" s="1">
+        <v>10</v>
+      </c>
+      <c r="T5" s="1">
+        <v>2</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="V5" s="1">
+        <v>1</v>
+      </c>
+      <c r="W5" s="1">
+        <v>20</v>
+      </c>
+      <c r="X5" s="1">
+        <v>100</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
+      <c r="A6">
+        <v>1000003</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="1">
+        <v>3</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L6" s="1">
+        <v>60</v>
+      </c>
+      <c r="M6" s="1">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="S6" s="1">
+        <v>10</v>
+      </c>
+      <c r="T6" s="1">
+        <v>3</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="V6" s="1">
+        <v>2</v>
+      </c>
+      <c r="W6" s="1">
         <v>30</v>
       </c>
-      <c r="C3" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="51" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" s="51" t="s">
+      <c r="X6" s="1">
+        <v>150</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
+      <c r="A7">
+        <v>1000004</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J7" s="1">
+        <v>4</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="L7" s="1">
+        <v>60</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="S7" s="1">
+        <v>10</v>
+      </c>
+      <c r="T7" s="1">
+        <v>4</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="V7" s="1">
+        <v>2</v>
+      </c>
+      <c r="W7" s="1">
         <v>40</v>
       </c>
-      <c r="M3" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="O3" s="51" t="s">
-        <v>43</v>
-      </c>
-      <c r="P3" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="R3" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="S3" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="T3" s="51" t="s">
-        <v>48</v>
-      </c>
-      <c r="U3" s="51" t="s">
-        <v>49</v>
-      </c>
-      <c r="V3" s="51" t="s">
+      <c r="X7" s="1">
+        <v>200</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>4</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
+      <c r="A8">
+        <v>1000005</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="1">
+        <v>5</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="1">
+        <v>60</v>
+      </c>
+      <c r="M8" s="1">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="S8" s="1">
+        <v>10</v>
+      </c>
+      <c r="T8" s="1">
+        <v>5</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="V8" s="1">
+        <v>2</v>
+      </c>
+      <c r="W8" s="1">
         <v>50</v>
       </c>
-      <c r="W3" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="X3" s="51" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y3" s="50" t="s">
-        <v>53</v>
+      <c r="X8" s="1">
+        <v>250</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>5</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="50">
-        <v>1000001</v>
-      </c>
-      <c r="B4" s="50">
-        <v>1</v>
-      </c>
-      <c r="C4" s="51">
-        <v>1</v>
-      </c>
-      <c r="D4" s="51" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="51" t="s">
+    <row r="9" spans="1:27">
+      <c r="A9">
+        <v>1000006</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="F9" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="1">
+        <v>6</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="L9" s="1">
         <v>60</v>
       </c>
-      <c r="K4" s="51">
-        <v>1</v>
-      </c>
-      <c r="L4" s="51" t="s">
+      <c r="M9" s="1">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="S9" s="1">
+        <v>10</v>
+      </c>
+      <c r="T9" s="1">
+        <v>6</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="V9" s="1">
+        <v>3</v>
+      </c>
+      <c r="W9" s="1">
+        <v>60</v>
+      </c>
+      <c r="X9" s="1">
+        <v>300</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>6</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
+      <c r="A10">
+        <v>1000007</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="51">
-        <v>1</v>
-      </c>
-      <c r="N4" s="51">
-        <v>1</v>
-      </c>
-      <c r="O4" s="51">
-        <v>5</v>
-      </c>
-      <c r="P4" s="51">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="51">
+      <c r="F10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" s="1">
+        <v>60</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="S10" s="1">
         <v>10</v>
       </c>
-      <c r="R4" s="51">
-        <v>1</v>
-      </c>
-      <c r="S4" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="T4" s="51">
-        <v>1</v>
-      </c>
-      <c r="U4" s="51">
+      <c r="T10" s="1">
+        <v>7</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="V10" s="1">
+        <v>3</v>
+      </c>
+      <c r="W10" s="1">
+        <v>70</v>
+      </c>
+      <c r="X10" s="1">
+        <v>350</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>7</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
+      <c r="A11">
+        <v>1000008</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="1">
+        <v>8</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="L11" s="1">
+        <v>60</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="S11" s="1">
         <v>10</v>
       </c>
-      <c r="V4" s="51">
-        <v>50</v>
-      </c>
-      <c r="W4" s="51">
-        <v>1</v>
-      </c>
-      <c r="X4" s="51" t="s">
+      <c r="T11" s="1">
+        <v>8</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="V11" s="1">
+        <v>3</v>
+      </c>
+      <c r="W11" s="1">
+        <v>80</v>
+      </c>
+      <c r="X11" s="1">
+        <v>400</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>8</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
+      <c r="A12">
+        <v>1000009</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Y4" s="50" t="s">
+      <c r="J12" s="1">
+        <v>9</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L12" s="1">
+        <v>60</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="P12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="S12" s="1">
+        <v>10</v>
+      </c>
+      <c r="T12" s="1">
+        <v>9</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="V12" s="1">
+        <v>4</v>
+      </c>
+      <c r="W12" s="1">
+        <v>90</v>
+      </c>
+      <c r="X12" s="1">
+        <v>450</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>9</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" s="50">
-        <v>1000002</v>
-      </c>
-      <c r="B5" s="50">
-        <v>1</v>
-      </c>
-      <c r="C5" s="51">
-        <v>2</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="51">
-        <v>20</v>
-      </c>
-      <c r="J5" s="51">
+    <row r="13" spans="1:27">
+      <c r="A13">
+        <v>1000010</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13" s="1">
+        <v>10</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="L13" s="1">
         <v>60</v>
       </c>
-      <c r="K5" s="51">
-        <v>1</v>
-      </c>
-      <c r="L5" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="M5" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N5" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="O5" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" s="51">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="51">
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="S13" s="1">
         <v>10</v>
       </c>
-      <c r="R5" s="51">
-        <v>2</v>
-      </c>
-      <c r="S5" s="51" t="s">
-        <v>71</v>
-      </c>
-      <c r="T5" s="51">
-        <v>1</v>
-      </c>
-      <c r="U5" s="51">
-        <v>20</v>
-      </c>
-      <c r="V5" s="51">
+      <c r="T13" s="1">
+        <v>10</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="V13" s="1">
+        <v>4</v>
+      </c>
+      <c r="W13" s="1">
         <v>100</v>
       </c>
-      <c r="W5" s="51">
-        <v>2</v>
-      </c>
-      <c r="X5" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="Y5" s="50" t="s">
-        <v>73</v>
+      <c r="X13" s="1">
+        <v>500</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>10</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>147</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="50">
-        <v>1000003</v>
-      </c>
-      <c r="B6" s="50">
-        <v>1</v>
-      </c>
-      <c r="C6" s="51">
-        <v>3</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="G6" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="H6" s="51">
-        <v>3</v>
-      </c>
-      <c r="I6" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="J6" s="51">
-        <v>60</v>
-      </c>
-      <c r="K6" s="51">
-        <v>1</v>
-      </c>
-      <c r="L6" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="M6" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="O6" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="P6" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q6" s="51">
-        <v>10</v>
-      </c>
-      <c r="R6" s="51">
-        <v>3</v>
-      </c>
-      <c r="S6" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="T6" s="51">
-        <v>2</v>
-      </c>
-      <c r="U6" s="51">
-        <v>30</v>
-      </c>
-      <c r="V6" s="51">
-        <v>150</v>
-      </c>
-      <c r="W6" s="51">
-        <v>3</v>
-      </c>
-      <c r="X6" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y6" s="50" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="50">
-        <v>1000004</v>
-      </c>
-      <c r="B7" s="50">
-        <v>1</v>
-      </c>
-      <c r="C7" s="51">
-        <v>4</v>
-      </c>
-      <c r="D7" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="G7" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="H7" s="51">
-        <v>4</v>
-      </c>
-      <c r="I7" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="J7" s="51">
-        <v>60</v>
-      </c>
-      <c r="K7" s="51">
-        <v>1</v>
-      </c>
-      <c r="L7" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="M7" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="O7" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="P7" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q7" s="51">
-        <v>10</v>
-      </c>
-      <c r="R7" s="51">
-        <v>4</v>
-      </c>
-      <c r="S7" s="51" t="s">
-        <v>91</v>
-      </c>
-      <c r="T7" s="51">
-        <v>2</v>
-      </c>
-      <c r="U7" s="51">
-        <v>40</v>
-      </c>
-      <c r="V7" s="51">
-        <v>200</v>
-      </c>
-      <c r="W7" s="51">
-        <v>4</v>
-      </c>
-      <c r="X7" s="51" t="s">
-        <v>92</v>
-      </c>
-      <c r="Y7" s="50" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="50">
-        <v>1000005</v>
-      </c>
-      <c r="B8" s="50">
-        <v>1</v>
-      </c>
-      <c r="C8" s="51">
-        <v>5</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="H8" s="51">
-        <v>5</v>
-      </c>
-      <c r="I8" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="J8" s="51">
-        <v>60</v>
-      </c>
-      <c r="K8" s="51">
-        <v>1</v>
-      </c>
-      <c r="L8" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="M8" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="O8" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="P8" s="53" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q8" s="51">
-        <v>10</v>
-      </c>
-      <c r="R8" s="51">
-        <v>5</v>
-      </c>
-      <c r="S8" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="T8" s="51">
-        <v>2</v>
-      </c>
-      <c r="U8" s="51">
-        <v>50</v>
-      </c>
-      <c r="V8" s="51">
-        <v>250</v>
-      </c>
-      <c r="W8" s="51">
-        <v>5</v>
-      </c>
-      <c r="X8" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y8" s="50" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="50">
-        <v>1000006</v>
-      </c>
-      <c r="B9" s="50">
-        <v>1</v>
-      </c>
-      <c r="C9" s="51">
-        <v>6</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="G9" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="H9" s="51">
-        <v>6</v>
-      </c>
-      <c r="I9" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="51">
-        <v>60</v>
-      </c>
-      <c r="K9" s="51">
-        <v>1</v>
-      </c>
-      <c r="L9" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="M9" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="O9" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="P9" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q9" s="51">
-        <v>10</v>
-      </c>
-      <c r="R9" s="51">
-        <v>6</v>
-      </c>
-      <c r="S9" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="T9" s="51">
-        <v>3</v>
-      </c>
-      <c r="U9" s="51">
-        <v>60</v>
-      </c>
-      <c r="V9" s="51">
-        <v>300</v>
-      </c>
-      <c r="W9" s="51">
-        <v>6</v>
-      </c>
-      <c r="X9" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y9" s="50" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="50">
-        <v>1000007</v>
-      </c>
-      <c r="B10" s="50">
-        <v>1</v>
-      </c>
-      <c r="C10" s="51">
-        <v>7</v>
-      </c>
-      <c r="D10" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="51">
-        <v>7</v>
-      </c>
-      <c r="I10" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="J10" s="51">
-        <v>60</v>
-      </c>
-      <c r="K10" s="51">
-        <v>1</v>
-      </c>
-      <c r="L10" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="M10" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N10" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="O10" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="P10" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q10" s="51">
-        <v>10</v>
-      </c>
-      <c r="R10" s="51">
-        <v>7</v>
-      </c>
-      <c r="S10" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="T10" s="51">
-        <v>3</v>
-      </c>
-      <c r="U10" s="51">
-        <v>70</v>
-      </c>
-      <c r="V10" s="51">
-        <v>350</v>
-      </c>
-      <c r="W10" s="51">
-        <v>7</v>
-      </c>
-      <c r="X10" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y10" s="50" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="50">
-        <v>1000008</v>
-      </c>
-      <c r="B11" s="50">
-        <v>1</v>
-      </c>
-      <c r="C11" s="51">
-        <v>8</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="G11" s="51" t="s">
-        <v>119</v>
-      </c>
-      <c r="H11" s="51">
-        <v>8</v>
-      </c>
-      <c r="I11" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="J11" s="51">
-        <v>60</v>
-      </c>
-      <c r="K11" s="51">
-        <v>1</v>
-      </c>
-      <c r="L11" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="M11" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N11" s="51" t="s">
-        <v>122</v>
-      </c>
-      <c r="O11" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="P11" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q11" s="51">
-        <v>10</v>
-      </c>
-      <c r="R11" s="51">
-        <v>8</v>
-      </c>
-      <c r="S11" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="T11" s="51">
-        <v>3</v>
-      </c>
-      <c r="U11" s="51">
-        <v>80</v>
-      </c>
-      <c r="V11" s="51">
-        <v>400</v>
-      </c>
-      <c r="W11" s="51">
-        <v>8</v>
-      </c>
-      <c r="X11" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y11" s="50" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="50">
-        <v>1000009</v>
-      </c>
-      <c r="B12" s="50">
-        <v>1</v>
-      </c>
-      <c r="C12" s="51">
-        <v>9</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="H12" s="51">
-        <v>9</v>
-      </c>
-      <c r="I12" s="51" t="s">
-        <v>129</v>
-      </c>
-      <c r="J12" s="51">
-        <v>60</v>
-      </c>
-      <c r="K12" s="51">
-        <v>1</v>
-      </c>
-      <c r="L12" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="M12" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N12" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="O12" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="P12" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q12" s="51">
-        <v>10</v>
-      </c>
-      <c r="R12" s="51">
-        <v>9</v>
-      </c>
-      <c r="S12" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="T12" s="51">
-        <v>4</v>
-      </c>
-      <c r="U12" s="51">
-        <v>90</v>
-      </c>
-      <c r="V12" s="51">
-        <v>450</v>
-      </c>
-      <c r="W12" s="51">
-        <v>9</v>
-      </c>
-      <c r="X12" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y12" s="50" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="50">
-        <v>1000010</v>
-      </c>
-      <c r="B13" s="50">
-        <v>1</v>
-      </c>
-      <c r="C13" s="51">
-        <v>10</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" s="51">
-        <v>10</v>
-      </c>
-      <c r="I13" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="J13" s="51">
-        <v>60</v>
-      </c>
-      <c r="K13" s="51">
-        <v>1</v>
-      </c>
-      <c r="L13" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="M13" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="O13" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="P13" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q13" s="51">
-        <v>10</v>
-      </c>
-      <c r="R13" s="51">
-        <v>10</v>
-      </c>
-      <c r="S13" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="T13" s="51">
-        <v>4</v>
-      </c>
-      <c r="U13" s="51">
-        <v>100</v>
-      </c>
-      <c r="V13" s="51">
-        <v>500</v>
-      </c>
-      <c r="W13" s="51">
-        <v>10</v>
-      </c>
-      <c r="X13" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y13" s="50" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="32" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="33" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="34" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="35" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="36" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="37" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="38" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="39" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="40" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="41" ht="15" customHeight="1" s="51" customFormat="1"/>
-    <row r="73" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="74" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="75" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="76" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="77" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="78" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="79" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="80" ht="12" customHeight="1" s="51" customFormat="1"/>
-    <row r="81" ht="12" customHeight="1" s="51" customFormat="1"/>
+    <row r="31" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="32" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="33" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="34" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="35" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="36" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="37" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="38" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="39" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="40" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="41" s="1" customFormat="1" ht="15" customHeight="1"/>
+    <row r="73" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="74" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="75" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="76" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="77" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="78" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="79" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="80" s="1" customFormat="1" ht="12" customHeight="1"/>
+    <row r="81" s="1" customFormat="1" ht="12" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_fight_type_conquer_info[战斗-征服模式].xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="127">
   <si>
     <t>id</t>
   </si>
@@ -226,12 +226,12 @@
     <t>1</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>100-150</t>
   </si>
   <si>
@@ -253,9 +253,6 @@
     <t>2</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>1.25</t>
   </si>
   <si>
@@ -277,12 +274,6 @@
     <t>1020020001&amp;1020030001&amp;1031010001&amp;1031020001</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>1.5</t>
   </si>
   <si>
@@ -310,15 +301,6 @@
     <t/>
   </si>
   <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>1.75</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -337,15 +319,9 @@
     <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1020020001&amp;1020030001&amp;1031030001&amp;1031040001</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
-    <t>5-6</t>
-  </si>
-  <si>
     <t>500-550</t>
   </si>
   <si>
@@ -361,15 +337,6 @@
     <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1031030001&amp;1031040001&amp;1041030001</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
     <t>600-650</t>
   </si>
   <si>
@@ -385,18 +352,9 @@
     <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1031030001&amp;1031040001&amp;1041030001&amp;1031050001</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
-    <t>1-6</t>
-  </si>
-  <si>
     <t>700-750</t>
   </si>
   <si>
@@ -409,15 +367,6 @@
     <t>1041010001&amp;1041020001&amp;1031010001&amp;1031020001&amp;1031030001&amp;1031040001&amp;1041030001&amp;1031050001&amp;1031080001</t>
   </si>
   <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>3.5</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
@@ -436,9 +385,6 @@
     <t>1041010001&amp;1041020001&amp;1041030001&amp;1031050001&amp;1031080001&amp;1031010002</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
@@ -455,15 +401,6 @@
   </si>
   <si>
     <t>1041010001&amp;1041020001&amp;1041030001&amp;1031050001&amp;1031080001&amp;1031010002&amp;1041010003</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>4.5</t>
   </si>
   <si>
     <t>14</t>
@@ -1470,10 +1407,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1548,15 +1485,15 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1631,15 +1568,15 @@
       <c r="Z2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1714,15 +1651,15 @@
       <c r="Z3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AA3" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>1000001</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4" s="1">
@@ -1746,17 +1683,17 @@
       <c r="J4" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="K4" s="1">
+        <v>10</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="O4" s="1">
         <v>1</v>
@@ -1794,15 +1731,15 @@
       <c r="Z4" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AA4" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>1000002</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1">
@@ -1835,17 +1772,17 @@
       <c r="M5" s="1">
         <v>1</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>73</v>
+      <c r="N5" s="1">
+        <v>20</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>63</v>
       </c>
       <c r="P5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="R5" s="1">
         <v>3</v>
@@ -1857,7 +1794,7 @@
         <v>2</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="V5" s="1">
         <v>1</v>
@@ -1872,17 +1809,17 @@
         <v>2</v>
       </c>
       <c r="Z5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AA5" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>1000003</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1">
@@ -1895,10 +1832,10 @@
         <v>59</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>62</v>
@@ -1906,8 +1843,8 @@
       <c r="J6" s="1">
         <v>3</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>81</v>
+      <c r="K6" s="1">
+        <v>40</v>
       </c>
       <c r="L6" s="1">
         <v>60</v>
@@ -1915,20 +1852,20 @@
       <c r="M6" s="1">
         <v>1</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>82</v>
+      <c r="N6" s="1">
+        <v>30</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>63</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="S6" s="1">
         <v>10</v>
@@ -1937,7 +1874,7 @@
         <v>3</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="V6" s="1">
         <v>2</v>
@@ -1952,17 +1889,17 @@
         <v>3</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>88</v>
+        <v>84</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>1000004</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1">
@@ -1975,22 +1912,22 @@
         <v>59</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>62</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J7" s="1">
         <v>4</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>92</v>
+      <c r="K7" s="1">
+        <v>60</v>
       </c>
       <c r="L7" s="1">
         <v>60</v>
@@ -1998,17 +1935,17 @@
       <c r="M7" s="1">
         <v>1</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>93</v>
+      <c r="N7" s="1">
+        <v>40</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="P7" s="1" t="s">
-        <v>94</v>
+      <c r="P7" s="1">
+        <v>2</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="R7" s="3" t="s">
         <v>62</v>
@@ -2020,7 +1957,7 @@
         <v>4</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="V7" s="1">
         <v>2</v>
@@ -2035,17 +1972,17 @@
         <v>4</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>98</v>
+        <v>91</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>1000005</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1">
@@ -2058,10 +1995,10 @@
         <v>59</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>62</v>
@@ -2069,8 +2006,8 @@
       <c r="J8" s="1">
         <v>5</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>65</v>
+      <c r="K8" s="1">
+        <v>80</v>
       </c>
       <c r="L8" s="1">
         <v>60</v>
@@ -2078,20 +2015,20 @@
       <c r="M8" s="1">
         <v>1</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>101</v>
+      <c r="N8" s="1">
+        <v>50</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="P8" s="1" t="s">
-        <v>72</v>
+      <c r="P8" s="1">
+        <v>2.5</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="S8" s="1">
         <v>10</v>
@@ -2100,7 +2037,7 @@
         <v>5</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="V8" s="1">
         <v>2</v>
@@ -2115,17 +2052,17 @@
         <v>5</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>106</v>
+        <v>97</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>1000006</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1">
@@ -2138,10 +2075,10 @@
         <v>59</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>62</v>
@@ -2149,8 +2086,8 @@
       <c r="J9" s="1">
         <v>6</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>109</v>
+      <c r="K9" s="1">
+        <v>100</v>
       </c>
       <c r="L9" s="1">
         <v>60</v>
@@ -2158,20 +2095,20 @@
       <c r="M9" s="1">
         <v>1</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>110</v>
+      <c r="N9" s="1">
+        <v>60</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>111</v>
+      <c r="P9" s="1">
+        <v>3</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="S9" s="1">
         <v>10</v>
@@ -2180,7 +2117,7 @@
         <v>6</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="V9" s="1">
         <v>3</v>
@@ -2195,17 +2132,17 @@
         <v>6</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>114</v>
+        <v>102</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>1000007</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1">
@@ -2218,10 +2155,10 @@
         <v>59</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>62</v>
@@ -2229,8 +2166,8 @@
       <c r="J10" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>117</v>
+      <c r="K10" s="1">
+        <v>120</v>
       </c>
       <c r="L10" s="1">
         <v>60</v>
@@ -2238,20 +2175,20 @@
       <c r="M10" s="1">
         <v>1</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>81</v>
+      <c r="N10" s="1">
+        <v>70</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="P10" s="1" t="s">
-        <v>118</v>
+      <c r="P10" s="1">
+        <v>3.5</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="S10" s="1">
         <v>10</v>
@@ -2260,7 +2197,7 @@
         <v>7</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="V10" s="1">
         <v>3</v>
@@ -2275,17 +2212,17 @@
         <v>7</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>123</v>
+        <v>108</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>1000008</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>1</v>
       </c>
       <c r="C11" s="1">
@@ -2298,10 +2235,10 @@
         <v>59</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>62</v>
@@ -2309,8 +2246,8 @@
       <c r="J11" s="1">
         <v>8</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>125</v>
+      <c r="K11" s="1">
+        <v>140</v>
       </c>
       <c r="L11" s="1">
         <v>60</v>
@@ -2318,20 +2255,20 @@
       <c r="M11" s="1">
         <v>1</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>126</v>
+      <c r="N11" s="1">
+        <v>80</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="P11" s="1" t="s">
-        <v>127</v>
+      <c r="P11" s="1">
+        <v>4</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="S11" s="1">
         <v>10</v>
@@ -2340,7 +2277,7 @@
         <v>8</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="V11" s="1">
         <v>3</v>
@@ -2355,17 +2292,17 @@
         <v>8</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>131</v>
+        <v>113</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12">
+      <c r="A12" s="1">
         <v>1000009</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>1</v>
       </c>
       <c r="C12" s="1">
@@ -2378,10 +2315,10 @@
         <v>59</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>62</v>
@@ -2389,8 +2326,8 @@
       <c r="J12" s="1">
         <v>9</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>134</v>
+      <c r="K12" s="1">
+        <v>160</v>
       </c>
       <c r="L12" s="1">
         <v>60</v>
@@ -2398,20 +2335,20 @@
       <c r="M12" s="1">
         <v>1</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>92</v>
+      <c r="N12" s="1">
+        <v>90</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="P12" s="1" t="s">
-        <v>85</v>
+      <c r="P12" s="1">
+        <v>4.5</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="S12" s="1">
         <v>10</v>
@@ -2420,7 +2357,7 @@
         <v>9</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="V12" s="1">
         <v>4</v>
@@ -2435,17 +2372,17 @@
         <v>9</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>138</v>
+        <v>119</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>1000010</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>1</v>
       </c>
       <c r="C13" s="1">
@@ -2458,10 +2395,10 @@
         <v>59</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>62</v>
@@ -2469,8 +2406,8 @@
       <c r="J13" s="1">
         <v>10</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>141</v>
+      <c r="K13" s="1">
+        <v>110180</v>
       </c>
       <c r="L13" s="1">
         <v>60</v>
@@ -2478,20 +2415,20 @@
       <c r="M13" s="1">
         <v>1</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>142</v>
+      <c r="N13" s="1">
+        <v>100</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="P13" s="1" t="s">
-        <v>143</v>
+      <c r="P13" s="1">
+        <v>5</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="S13" s="1">
         <v>10</v>
@@ -2500,7 +2437,7 @@
         <v>10</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="V13" s="1">
         <v>4</v>
@@ -2515,10 +2452,10 @@
         <v>10</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>147</v>
+        <v>125</v>
+      </c>
+      <c r="AA13" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="15" customHeight="1"/>
